--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3055" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2939" uniqueCount="454">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T07:17:44+00:00</t>
+    <t>2023-05-10T08:50:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>Global (Whole world)</t>
+    <t>World</t>
   </si>
   <si>
     <t>Description</t>
@@ -93,7 +93,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.0.1</t>
+    <t>5.0.0</t>
   </si>
   <si>
     <t>Kind</t>
@@ -237,13 +237,13 @@
     <t>Mapping: Workflow Pattern</t>
   </si>
   <si>
-    <t>Mapping: HL7 v2 Mapping</t>
+    <t>Mapping: FiveWs Pattern Mapping</t>
+  </si>
+  <si>
+    <t>Mapping: HL7 V2 Mapping</t>
   </si>
   <si>
     <t>Mapping: RIM Mapping</t>
-  </si>
-  <si>
-    <t>Mapping: FiveWs Pattern Mapping</t>
   </si>
   <si>
     <t/>
@@ -259,22 +259,25 @@
 </t>
   </si>
   <si>
-    <t>A healthcare consumer's  choices to permit or deny recipients or roles to perform actions for specific purposes and periods of time</t>
-  </si>
-  <si>
-    <t>A record of a healthcare consumer’s  choices, which permits or denies identified recipient(s) or recipient role(s) to perform one or more actions within a given policy context, for specific purposes and periods of time.</t>
-  </si>
-  <si>
-    <t>Broadly, there are 3 key areas of consent for patients: Consent around sharing information (aka Privacy Consent Directive - Authorization to Collect, Use, or Disclose information), consent for specific treatment, or kinds of treatment, and general advance care directives.</t>
+    <t>A healthcare consumer's  or third party's choices to permit or deny recipients or roles to perform actions for specific purposes and periods of time</t>
+  </si>
+  <si>
+    <t>A record of a healthcare consumer’s  choices  or choices made on their behalf by a third party, which permits or denies identified recipient(s) or recipient role(s) to perform one or more actions within a given policy context, for specific purposes and periods of time.</t>
+  </si>
+  <si>
+    <t>Broadly, there are 3 key areas of consent for patients: Consent around sharing information (aka Privacy Consent Directive - Authorization to Collect, Use, or Disclose information), consent for specific treatment, or kinds of treatment and consent for research participation and data sharing.</t>
   </si>
   <si>
     <t>Event</t>
   </si>
   <si>
+    <t>infrastructure.information</t>
+  </si>
+  <si>
     <t>CON</t>
   </si>
   <si>
-    <t>FinancialConsent</t>
+    <t>Entity, Role, or Act</t>
   </si>
   <si>
     <t>Consent.id</t>
@@ -296,7 +299,7 @@
     <t>The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
   </si>
   <si>
-    <t>The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
+    <t>Within the context of the FHIR RESTful interactions, the resource has an id except for cases like the create and conditional update. Otherwise, the use of the resouce id depends on the given use case.</t>
   </si>
   <si>
     <t>Resource.id</t>
@@ -335,7 +338,7 @@
     <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
   </si>
   <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of its narrative along with other profiles, value sets, etc.</t>
   </si>
   <si>
     <t>Resource.implicitRules</t>
@@ -357,13 +360,13 @@
     <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
   </si>
   <si>
-    <t>preferred</t>
-  </si>
-  <si>
-    <t>A human language.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>required</t>
+  </si>
+  <si>
+    <t>IETF language tag for a human language</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/all-languages|5.0.0</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -386,10 +389,14 @@
     <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
   </si>
   <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+    <t>Contained resources do not have a narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
   </si>
   <si>
     <t>DomainResource.text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dom-6
+</t>
   </si>
   <si>
     <t>Act.text?</t>
@@ -409,13 +416,17 @@
     <t>Contained, inline Resources</t>
   </si>
   <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, nor can they have their own independent transaction scope. This is allowed to be a Parameters resource if and only if it is referenced by a resource that provides context/meaning.</t>
+  </si>
+  <si>
+    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags in their meta elements, but SHALL NOT have security labels.</t>
   </si>
   <si>
     <t>DomainResource.contained</t>
+  </si>
+  <si>
+    <t>dom-2
+dom-4dom-3dom-5</t>
   </si>
   <si>
     <t>N/A</t>
@@ -435,7 +446,7 @@
     <t>Additional content defined by implementations</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
@@ -454,11 +465,11 @@
     <t>Extensions that cannot be ignored</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R5/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -480,224 +491,227 @@
     <t>This identifier identifies this copy of the consent. Where this identifier is also used elsewhere as the identifier for a consent record (e.g. a CDA consent document) then the consent details are expected to be the same.</t>
   </si>
   <si>
-    <t>&lt;valueIdentifier xmlns="http://hl7.org/fhir"&gt;
-  &lt;system value="urn:ietf:rfc:3986"/&gt;
-  &lt;value value="Local eCMS identifier"/&gt;
-&lt;/valueIdentifier&gt;</t>
-  </si>
-  <si>
     <t>Event.identifier</t>
   </si>
   <si>
-    <t>.id</t>
-  </si>
-  <si>
     <t>FiveWs.identifier</t>
   </si>
   <si>
+    <t>CON-4 (Consent Form Number – EI)
+Note: An implementation-specific requirement will be needed</t>
+  </si>
+  <si>
     <t>Consent.status</t>
   </si>
   <si>
-    <t>draft | proposed | active | rejected | inactive | entered-in-error</t>
-  </si>
-  <si>
-    <t>Indicates the current state of this consent.</t>
+    <t>draft | active | inactive | not-done | entered-in-error | unknown</t>
+  </si>
+  <si>
+    <t>Indicates the current state of this Consent resource.</t>
   </si>
   <si>
     <t>This element is labeled as a modifier because the status contains the codes rejected and entered-in-error that mark the Consent as not currently valid.</t>
   </si>
   <si>
-    <t>The Consent Directive that is pointed to might be in various lifecycle states, e.g., a revoked Consent Directive.</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
     <t>Indicates the state of the consent.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-state-codes|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/consent-state-codes|5.0.0</t>
   </si>
   <si>
     <t>Event.status</t>
   </si>
   <si>
-    <t>HL7 Table 0498 - Consent Status</t>
-  </si>
-  <si>
-    <t>.statusCode</t>
-  </si>
-  <si>
     <t>FiveWs.status</t>
   </si>
   <si>
-    <t>Consent.scope</t>
+    <t>CON-11 (Consent Status – CNE using table HL70498)</t>
+  </si>
+  <si>
+    <t>Consent.category</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept
 </t>
   </si>
   <si>
-    <t>Which of the four areas this resource covers (extensible)</t>
-  </si>
-  <si>
-    <t>A selector of the type of consent being presented: ADR, Privacy, Treatment, Research.  This list is now extensible.</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>The four anticipated uses for the Consent Resource.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-scope</t>
-  </si>
-  <si>
-    <t>Consent.scope.id</t>
+    <t>Classification of the consent statement - for indexing/retrieval</t>
+  </si>
+  <si>
+    <t>A classification of the type of consents found in the statement. This element supports indexing and retrieval of consent statements.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>A classification of the type of consents found in a consent statement.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/consent-category</t>
+  </si>
+  <si>
+    <t>Event.code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>CON-2 (Consent Type - CWE using table HL70496)</t>
+  </si>
+  <si>
+    <t>Consent.category.id</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Consent.category.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Consent.category.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>Consent.category.coding.id</t>
+  </si>
+  <si>
+    <t>Consent.category.coding.extension</t>
+  </si>
+  <si>
+    <t>Consent.category.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should be an absolute reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>http://loinc.org</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>Consent.category.coding.version</t>
   </si>
   <si>
     <t xml:space="preserve">string
 </t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Consent.scope.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Consent.category.coding.code</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>59284-0</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cod-1
 </t>
   </si>
   <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>Consent.scope.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>Consent.scope.coding.id</t>
-  </si>
-  <si>
-    <t>Consent.scope.coding.extension</t>
-  </si>
-  <si>
-    <t>Consent.scope.coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/CodeSystem/consentscope</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>Consent.scope.coding.version</t>
-  </si>
-  <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>Consent.scope.coding.code</t>
-  </si>
-  <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>patient-privacy</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
     <t>C*E.1</t>
   </si>
   <si>
     <t>./code</t>
   </si>
   <si>
-    <t>Consent.scope.coding.display</t>
+    <t>Consent.category.coding.display</t>
   </si>
   <si>
     <t>Representation defined by the system</t>
@@ -718,7 +732,7 @@
     <t>CV.displayName</t>
   </si>
   <si>
-    <t>Consent.scope.coding.userSelected</t>
+    <t>Consent.category.coding.userSelected</t>
   </si>
   <si>
     <t xml:space="preserve">boolean
@@ -746,7 +760,7 @@
     <t>CD.codingRationale</t>
   </si>
   <si>
-    <t>Consent.scope.text</t>
+    <t>Consent.category.text</t>
   </si>
   <si>
     <t>Plain text representation of the concept</t>
@@ -770,73 +784,7 @@
     <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
-    <t>Consent.category</t>
-  </si>
-  <si>
-    <t>Classification of the consent statement - for indexing/retrieval</t>
-  </si>
-  <si>
-    <t>A classification of the type of consents found in the statement. This element supports indexing and retrieval of consent statements.</t>
-  </si>
-  <si>
-    <t>A classification of the type of consents found in a consent statement.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-category</t>
-  </si>
-  <si>
-    <t>Event.code</t>
-  </si>
-  <si>
-    <t>HL7 Table 0497 - Consent Type</t>
-  </si>
-  <si>
-    <t>CNTRCT</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>Consent.category.id</t>
-  </si>
-  <si>
-    <t>Consent.category.extension</t>
-  </si>
-  <si>
-    <t>Consent.category.coding</t>
-  </si>
-  <si>
-    <t>Consent.category.coding.id</t>
-  </si>
-  <si>
-    <t>Consent.category.coding.extension</t>
-  </si>
-  <si>
-    <t>Consent.category.coding.system</t>
-  </si>
-  <si>
-    <t>http://loinc.org</t>
-  </si>
-  <si>
-    <t>Consent.category.coding.version</t>
-  </si>
-  <si>
-    <t>Consent.category.coding.code</t>
-  </si>
-  <si>
-    <t>59284-0</t>
-  </si>
-  <si>
-    <t>Consent.category.coding.display</t>
-  </si>
-  <si>
-    <t>Consent.category.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Consent.category.text</t>
-  </si>
-  <si>
-    <t>Consent.patient</t>
+    <t>Consent.subject</t>
   </si>
   <si>
     <t xml:space="preserve">Reference(Patient)
@@ -846,261 +794,364 @@
     <t>Who the consent applies to</t>
   </si>
   <si>
-    <t>The patient/healthcare consumer to whom this consent applies.</t>
-  </si>
-  <si>
-    <t>Commonly, the patient the consent pertains to is the author, but for young and old people, it may be some other person.</t>
+    <t>The patient/healthcare practitioner or group of persons to whom this consent applies.</t>
   </si>
   <si>
     <t>Event.subject</t>
   </si>
   <si>
-    <t>Role</t>
-  </si>
-  <si>
-    <t>FiveWs.subject</t>
-  </si>
-  <si>
-    <t>Consent.dateTime</t>
+    <t>FiveWs.subject[x]</t>
+  </si>
+  <si>
+    <t>Consent.date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">date
+</t>
+  </si>
+  <si>
+    <t>Fully executed date of the consent</t>
+  </si>
+  <si>
+    <t>Date the consent instance was agreed to.</t>
+  </si>
+  <si>
+    <t>Event.occurrence[x]</t>
+  </si>
+  <si>
+    <t>FiveWs.recorded</t>
+  </si>
+  <si>
+    <t>CON-13 (Consent Decision Date/Time – DTM)</t>
+  </si>
+  <si>
+    <t>Consent.period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">period
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>Effective period for this Consent</t>
+  </si>
+  <si>
+    <t>Effective period for this Consent Resource and all provisions unless specified in that provision.</t>
+  </si>
+  <si>
+    <t>Consent.grantor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">grantor
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(CareTeam|HealthcareService|Organization|Patient|Practitioner|RelatedPerson|PractitionerRole)
+</t>
+  </si>
+  <si>
+    <t>Who is granting rights according to the policy and rules</t>
+  </si>
+  <si>
+    <t>The entity responsible for granting the rights listed in a Consent Directive.</t>
+  </si>
+  <si>
+    <t>Consent.grantee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">grantee
+</t>
+  </si>
+  <si>
+    <t>Who is agreeing to the policy and rules</t>
+  </si>
+  <si>
+    <t>The entity responsible for complying with the Consent Directive, including any obligations or limitations on authorizations and enforcement of prohibitions.</t>
+  </si>
+  <si>
+    <t>In a fully computable consent, both grantee and grantor  will be listed as actors within the consent. The Grantee and Grantor elements are for ease of search only.</t>
+  </si>
+  <si>
+    <t>Consent.manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">manager
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(HealthcareService|Organization|Patient|Practitioner)
+</t>
+  </si>
+  <si>
+    <t>Consent workflow management</t>
+  </si>
+  <si>
+    <t>The actor that manages the consent through its lifecycle.</t>
+  </si>
+  <si>
+    <t>FiveWs.witness</t>
+  </si>
+  <si>
+    <t>Consent.controller</t>
+  </si>
+  <si>
+    <t xml:space="preserve">controller
+</t>
+  </si>
+  <si>
+    <t>Consent Enforcer</t>
+  </si>
+  <si>
+    <t>The actor that controls/enforces the access according to the consent.</t>
+  </si>
+  <si>
+    <t>Consent.sourceAttachment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attachment
+</t>
+  </si>
+  <si>
+    <t>Source from which this consent is taken</t>
+  </si>
+  <si>
+    <t>The source on which this consent statement is based. The source might be a scanned original paper form.</t>
+  </si>
+  <si>
+    <t>The source can be contained inline (Attachment), referenced directly (Consent), referenced in a consent repository (DocumentReference), or simply by an identifier (Identifier), e.g. a CDA document id.</t>
+  </si>
+  <si>
+    <t>Potential mappings to CON-5,6,7,8,16,19, 20-23</t>
+  </si>
+  <si>
+    <t>Consent.sourceReference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Consent|DocumentReference|Contract|QuestionnaireResponse)
+</t>
+  </si>
+  <si>
+    <t>A reference to a consent that links back to such a source, a reference to a document repository (e.g. XDS) that stores the original consent document.</t>
+  </si>
+  <si>
+    <t>Consent.regulatoryBasis</t>
+  </si>
+  <si>
+    <t>Regulations establishing base Consent</t>
+  </si>
+  <si>
+    <t>A set of codes that indicate the regulatory basis (if any) that this consent supports.</t>
+  </si>
+  <si>
+    <t>http://openhie.org/fhir/rwanda-hiv/ValueSet/vs-patient-consent-for-sms-notifications</t>
+  </si>
+  <si>
+    <t>CON-3 (Consent Form ID and Version – ST)
+Note: An implementation-specific requirement will be needed</t>
+  </si>
+  <si>
+    <t>Consent.regulatoryBasis.id</t>
+  </si>
+  <si>
+    <t>Consent.regulatoryBasis.extension</t>
+  </si>
+  <si>
+    <t>Consent.regulatoryBasis.coding</t>
+  </si>
+  <si>
+    <t>Consent.regulatoryBasis.text</t>
+  </si>
+  <si>
+    <t>Consent policy</t>
+  </si>
+  <si>
+    <t>Consent.policyBasis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BackboneElement
+</t>
+  </si>
+  <si>
+    <t>Computable version of the backing policy</t>
+  </si>
+  <si>
+    <t>A Reference or URL used to uniquely identify the policy the organization will enforce for this Consent. This Reference or URL should be specific to the version of the policy and should be dereferencable to a computable policy of some form.</t>
+  </si>
+  <si>
+    <t>Consent.policyBasis.id</t>
+  </si>
+  <si>
+    <t>Consent.policyBasis.extension</t>
+  </si>
+  <si>
+    <t>Consent.policyBasis.modifierExtension</t>
+  </si>
+  <si>
+    <t>extensions
+user contentmodifiers</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored even if unrecognized</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>BackboneElement.modifierExtension</t>
+  </si>
+  <si>
+    <t>Consent.policyBasis.reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Resource)
+</t>
+  </si>
+  <si>
+    <t>Reference backing policy resource</t>
+  </si>
+  <si>
+    <t>A Reference that identifies the policy the organization will enforce for this Consent.</t>
+  </si>
+  <si>
+    <t>While any resource may be used, Consent, PlanDefinition and Contract would be most frequent</t>
+  </si>
+  <si>
+    <t>Consent.policyBasis.url</t>
+  </si>
+  <si>
+    <t xml:space="preserve">url
+</t>
+  </si>
+  <si>
+    <t>URL to a computable backing policy</t>
+  </si>
+  <si>
+    <t>A URL that links to a computable version of the policy the organization will enforce for this Consent.</t>
+  </si>
+  <si>
+    <t>Consent.policyText</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(DocumentReference)
+</t>
+  </si>
+  <si>
+    <t>Human Readable Policy</t>
+  </si>
+  <si>
+    <t>A Reference to the human readable policy explaining the basis for the Consent.</t>
+  </si>
+  <si>
+    <t>Consent.verification</t>
+  </si>
+  <si>
+    <t>Consent Verified by patient or family</t>
+  </si>
+  <si>
+    <t>Whether a treatment instruction (e.g. artificial respiration: yes or no) was verified with the patient, his/her family or another authorized person.</t>
+  </si>
+  <si>
+    <t>Consent.verification.id</t>
+  </si>
+  <si>
+    <t>Consent.verification.extension</t>
+  </si>
+  <si>
+    <t>Consent.verification.modifierExtension</t>
+  </si>
+  <si>
+    <t>Consent.verification.verified</t>
+  </si>
+  <si>
+    <t>Has been verified</t>
+  </si>
+  <si>
+    <t>Has the instruction been verified.</t>
+  </si>
+  <si>
+    <t>Consent.verification.verificationType</t>
+  </si>
+  <si>
+    <t>Business case of verification</t>
+  </si>
+  <si>
+    <t>Extensible list of verification type starting with verification and re-validation.</t>
+  </si>
+  <si>
+    <t>This allows the verification element to hold multiple use cases including RelatedPerson verification of the Grantee decision and periodic re-validation of the consent.</t>
+  </si>
+  <si>
+    <t>Types of Verification/Validation.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/consent-verification</t>
+  </si>
+  <si>
+    <t>Consent.verification.verifiedBy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Organization|Practitioner|PractitionerRole)
+</t>
+  </si>
+  <si>
+    <t>Person conducting verification</t>
+  </si>
+  <si>
+    <t>The person who conducted the verification/validation of the Grantor decision.</t>
+  </si>
+  <si>
+    <t>Consent.verification.verifiedWith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Patient|RelatedPerson)
+</t>
+  </si>
+  <si>
+    <t>Person who verified</t>
+  </si>
+  <si>
+    <t>Who verified the instruction (Patient, Relative or other Authorized Person).</t>
+  </si>
+  <si>
+    <t>Consent.verification.verificationDate</t>
   </si>
   <si>
     <t xml:space="preserve">dateTime
 </t>
   </si>
   <si>
-    <t>When this Consent was created or indexed</t>
-  </si>
-  <si>
-    <t>When this  Consent was issued / created / indexed.</t>
-  </si>
-  <si>
-    <t>This is not the time of the original consent, but the time that this statement was made or derived.</t>
-  </si>
-  <si>
-    <t>Event.occurrence[x]</t>
-  </si>
-  <si>
-    <t>Field 13/ Consent Decision Date</t>
-  </si>
-  <si>
-    <t>FinancialConsent effectiveTime</t>
-  </si>
-  <si>
-    <t>FiveWs.recorded</t>
-  </si>
-  <si>
-    <t>Consent.performer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">consentor
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Organization|Patient|Practitioner|RelatedPerson|PractitionerRole)
-</t>
-  </si>
-  <si>
-    <t>Who is agreeing to the policy and rules</t>
-  </si>
-  <si>
-    <t>Either the Grantor, which is the entity responsible for granting the rights listed in a Consent Directive or the Grantee, which is the entity responsible for complying with the Consent Directive, including any obligations or limitations on authorizations and enforcement of prohibitions.</t>
-  </si>
-  <si>
-    <t>Commonly, the patient the consent pertains to is the consentor, but particularly for young and old people, it may be some other person - e.g. a legal guardian.</t>
-  </si>
-  <si>
-    <t>Event.performer</t>
-  </si>
-  <si>
-    <t>Field 24/ ConsenterID</t>
-  </si>
-  <si>
-    <t>FiveWs.actor</t>
-  </si>
-  <si>
-    <t>Consent.organization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">custodian
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Organization)
-</t>
-  </si>
-  <si>
-    <t>Custodian of the consent</t>
-  </si>
-  <si>
-    <t>The organization that manages the consent, and the framework within which it is executed.</t>
-  </si>
-  <si>
-    <t>FiveWs.witness</t>
-  </si>
-  <si>
-    <t>Consent.source[x]</t>
-  </si>
-  <si>
-    <t>Attachment
-Reference(Consent|DocumentReference|Contract|QuestionnaireResponse)</t>
-  </si>
-  <si>
-    <t>Source from which this consent is taken</t>
-  </si>
-  <si>
-    <t>The source on which this consent statement is based. The source might be a scanned original paper form, or a reference to a consent that links back to such a source, a reference to a document repository (e.g. XDS) that stores the original consent document.</t>
-  </si>
-  <si>
-    <t>The source can be contained inline (Attachment), referenced directly (Consent), referenced in a consent repository (DocumentReference), or simply by an identifier (Identifier), e.g. a CDA document id.</t>
-  </si>
-  <si>
-    <t>Field 19 Informational Material Supplied Indicator</t>
-  </si>
-  <si>
-    <t>Consent.policy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BackboneElement
-</t>
-  </si>
-  <si>
-    <t>Policies covered by this consent</t>
-  </si>
-  <si>
-    <t>The references to the policies that are included in this consent scope. Policies may be organizational, but are often defined jurisdictionally, or in law.</t>
-  </si>
-  <si>
-    <t>Consent.policy.id</t>
-  </si>
-  <si>
-    <t>Consent.policy.extension</t>
-  </si>
-  <si>
-    <t>Consent.policy.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user contentmodifiers</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>BackboneElement.modifierExtension</t>
-  </si>
-  <si>
-    <t>Consent.policy.authority</t>
-  </si>
-  <si>
-    <t>Enforcement source for policy</t>
-  </si>
-  <si>
-    <t>Entity or Organization having regulatory jurisdiction or accountability for  enforcing policies pertaining to Consent Directives.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ppc-1
-</t>
-  </si>
-  <si>
-    <t>Consent.policy.uri</t>
-  </si>
-  <si>
-    <t>Specific policy covered by this consent</t>
-  </si>
-  <si>
-    <t>This element is for discoverability / documentation and does not modify or qualify the policy rules.</t>
-  </si>
-  <si>
-    <t>Consent.policyRule</t>
-  </si>
-  <si>
-    <t>Regulation that this consents to</t>
-  </si>
-  <si>
-    <t>A reference to the specific base computable regulation or policy.</t>
-  </si>
-  <si>
-    <t>If the policyRule is absent, computable consent would need to be constructed from the elements of the Consent resource.</t>
-  </si>
-  <si>
-    <t>Might be a unique identifier of a policy set in XACML, or other rules engine.</t>
-  </si>
-  <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ValueSet/vs-patient-consent-for-sms-notifications</t>
-  </si>
-  <si>
-    <t>Consent.policyRule.id</t>
-  </si>
-  <si>
-    <t>Consent.policyRule.extension</t>
-  </si>
-  <si>
-    <t>Consent.policyRule.coding</t>
-  </si>
-  <si>
-    <t>Consent.policyRule.text</t>
-  </si>
-  <si>
-    <t>Consent policy</t>
-  </si>
-  <si>
-    <t>Consent.verification</t>
-  </si>
-  <si>
-    <t>Consent Verified by patient or family</t>
-  </si>
-  <si>
-    <t>Whether a treatment instruction (e.g. artificial respiration yes or no) was verified with the patient, his/her family or another authorized person.</t>
-  </si>
-  <si>
-    <t>Consent.verification.id</t>
-  </si>
-  <si>
-    <t>Consent.verification.extension</t>
-  </si>
-  <si>
-    <t>Consent.verification.modifierExtension</t>
-  </si>
-  <si>
-    <t>Consent.verification.verified</t>
-  </si>
-  <si>
-    <t>Has been verified</t>
-  </si>
-  <si>
-    <t>Has the instruction been verified.</t>
-  </si>
-  <si>
-    <t>Consent.verification.verifiedWith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Patient|RelatedPerson)
-</t>
-  </si>
-  <si>
-    <t>Person who verified</t>
-  </si>
-  <si>
-    <t>Who verified the instruction (Patient, Relative or other Authorized Person).</t>
-  </si>
-  <si>
-    <t>Consent.verification.verificationDate</t>
-  </si>
-  <si>
     <t>When consent verified</t>
   </si>
   <si>
-    <t>Date verification was collected.</t>
+    <t>Date(s) verification was collected.</t>
+  </si>
+  <si>
+    <t>Allows for history of verification/validation.</t>
+  </si>
+  <si>
+    <t>Consent.decision</t>
+  </si>
+  <si>
+    <t>deny | permit</t>
+  </si>
+  <si>
+    <t>Action to take - permit or deny - as default.</t>
+  </si>
+  <si>
+    <t>Sets the base decision for Consent to be either permit or deny, with provisions assumed to be a negation of the previous level.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/consent-provision-type|5.0.0</t>
   </si>
   <si>
     <t>Consent.provision</t>
   </si>
   <si>
-    <t>Constraints to the base Consent.policyRule</t>
+    <t>Constraints to the base Consent.policyRule/Consent.policy</t>
   </si>
   <si>
     <t>An exception to the base policy of this consent. An exception can be an addition or removal of access permissions.</t>
@@ -1115,41 +1166,28 @@
     <t>Consent.provision.modifierExtension</t>
   </si>
   <si>
-    <t>Consent.provision.type</t>
-  </si>
-  <si>
-    <t>deny | permit</t>
-  </si>
-  <si>
-    <t>Action  to take - permit or deny - when the rule conditions are met.  Not permitted in root rule, required in all nested rules.</t>
-  </si>
-  <si>
-    <t>How a rule statement is applied, such as adding additional consent or removing consent.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-provision-type|4.0.1</t>
-  </si>
-  <si>
     <t>Consent.provision.period</t>
   </si>
   <si>
-    <t xml:space="preserve">Period
-</t>
-  </si>
-  <si>
-    <t>Timeframe for this rule</t>
-  </si>
-  <si>
-    <t>The timeframe in this rule is valid.</t>
+    <t>Timeframe for this provision</t>
+  </si>
+  <si>
+    <t>Timeframe for this provision.</t>
+  </si>
+  <si>
+    <t>This is the bound effective time of the consent and should be in the base provision in the Consent resource.</t>
+  </si>
+  <si>
+    <t>CON-14&amp;15 (Consent Effective Date Time, Consent End DateTime)</t>
   </si>
   <si>
     <t>Consent.provision.actor</t>
   </si>
   <si>
-    <t>Who|what controlled by this rule (or group, by role)</t>
-  </si>
-  <si>
-    <t>Who or what is controlled by this rule. Use group to identify a set of actors by some property they share (e.g. 'admitting officers').</t>
+    <t>Who|what controlled by this provision (or group, by role)</t>
+  </si>
+  <si>
+    <t>Who or what is controlled by this provision. Use group to identify a set of actors by some property they share (e.g. 'admitting officers').</t>
   </si>
   <si>
     <t>There is no specific actor associated with the exception</t>
@@ -1173,10 +1211,13 @@
     <t>How the individual is involved in the resources content that is described in the exception.</t>
   </si>
   <si>
+    <t>extensible</t>
+  </si>
+  <si>
     <t>How an actor is involved in the consent considerations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-role-type</t>
+    <t>http://hl7.org/fhir/ValueSet/participation-role-type</t>
   </si>
   <si>
     <t>Consent.provision.actor.reference</t>
@@ -1195,10 +1236,10 @@
     <t>Consent.provision.action</t>
   </si>
   <si>
-    <t>Actions controlled by this rule</t>
-  </si>
-  <si>
-    <t>Actions controlled by this Rule.</t>
+    <t>Actions controlled by this provision</t>
+  </si>
+  <si>
+    <t>Actions controlled by this provision.</t>
   </si>
   <si>
     <t>Note that this is the direct action (not the grounds for the action covered in the purpose element). At present, the only action in the understood and tested scope of this resource is 'read'.</t>
@@ -1207,9 +1248,6 @@
     <t>all actions</t>
   </si>
   <si>
-    <t>example</t>
-  </si>
-  <si>
     <t>Detailed codes for the consent action.</t>
   </si>
   <si>
@@ -1228,19 +1266,19 @@
     <t>If the consent specifies a security label of "R" then it applies to all resources that are labeled "R" or lower. E.g. for Confidentiality, it's a high water mark. For other kinds of security labels, subsumption logic applies. When the purpose of use tag is on the data, access request purpose of use shall not conflict.</t>
   </si>
   <si>
-    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>Example Security Labels from the Healthcare Privacy and Security Classification System.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/security-label-examples</t>
   </si>
   <si>
     <t>Consent.provision.purpose</t>
   </si>
   <si>
-    <t>Context of activities covered by this rule</t>
-  </si>
-  <si>
-    <t>The context of the activities a user is taking - why the user is accessing the data - that are controlled by this rule.</t>
+    <t>Context of activities covered by this provision</t>
+  </si>
+  <si>
+    <t>The context of the activities a user is taking - why the user is accessing the data - that are controlled by this provision.</t>
   </si>
   <si>
     <t>When the purpose of use tag is on the data, access request purpose of use shall not conflict.</t>
@@ -1252,34 +1290,52 @@
     <t>http://terminology.hl7.org/ValueSet/v3-PurposeOfUse</t>
   </si>
   <si>
-    <t>Consent.provision.class</t>
-  </si>
-  <si>
-    <t>e.g. Resource Type, Profile, CDA, etc.</t>
-  </si>
-  <si>
-    <t>The class of information covered by this rule. The type can be a FHIR resource type, a profile on a type, or a CDA document, or some other type that indicates what sort of information the consent relates to.</t>
-  </si>
-  <si>
-    <t>Multiple types are or'ed together. The intention of the contentType element is that the codes refer to profiles or document types defined in a standard or an implementation guide somewhere.</t>
-  </si>
-  <si>
-    <t>The class (type) of information a consent rule covers.</t>
+    <t>Consent.provision.documentType</t>
+  </si>
+  <si>
+    <t>e.g. Resource Type, Profile, CDA, etc</t>
+  </si>
+  <si>
+    <t>The documentType(s) covered by this provision. The type can be a CDA document, or some other type that indicates what sort of information the consent relates to.</t>
+  </si>
+  <si>
+    <t>Multiple types are or'ed together. The intention of the documentType element is that the codes refer to document types defined in a standard somewhere.</t>
+  </si>
+  <si>
+    <t>preferred</t>
+  </si>
+  <si>
+    <t>The document type a consent provision covers.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/consent-content-class</t>
   </si>
   <si>
+    <t>Consent.provision.resourceType</t>
+  </si>
+  <si>
+    <t>e.g. Resource Type, Profile, etc</t>
+  </si>
+  <si>
+    <t>The resourceType(s) covered by this provision. The type can be a FHIR resource type or a profile on a type that indicates what information the consent relates to.</t>
+  </si>
+  <si>
+    <t>Multiple types are or'ed together. The intention of the resourceType element is that the codes refer to profiles or document types defined in a standard or an implementation guide somewhere.</t>
+  </si>
+  <si>
+    <t>The resource types a consent provision covers.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
+  </si>
+  <si>
     <t>Consent.provision.code</t>
   </si>
   <si>
     <t>e.g. LOINC or SNOMED CT code, etc. in the content</t>
   </si>
   <si>
-    <t>If this code is found in an instance, then the rule applies.</t>
-  </si>
-  <si>
-    <t>Typical use of this is a Document code with class = CDA.</t>
+    <t>If this code is found in an instance, then the provision applies.</t>
   </si>
   <si>
     <t>If this code is found in an instance, then the exception applies.</t>
@@ -1291,10 +1347,10 @@
     <t>Consent.provision.dataPeriod</t>
   </si>
   <si>
-    <t>Timeframe for data controlled by this rule</t>
-  </si>
-  <si>
-    <t>Clinical or Operational Relevant period of time that bounds the data controlled by this rule.</t>
+    <t>Timeframe for data controlled by this provision</t>
+  </si>
+  <si>
+    <t>Clinical or Operational Relevant period of time that bounds the data controlled by this provision.</t>
   </si>
   <si>
     <t>This has a different sense to the Consent.period - that is when the consent agreement holds. This is the time period of the data that is controlled by the agreement.</t>
@@ -1303,10 +1359,10 @@
     <t>Consent.provision.data</t>
   </si>
   <si>
-    <t>Data controlled by this rule</t>
-  </si>
-  <si>
-    <t>The resources controlled by this rule if specific resources are referenced.</t>
+    <t>Data controlled by this provision</t>
+  </si>
+  <si>
+    <t>The resources controlled by this provision if specific resources are referenced.</t>
   </si>
   <si>
     <t>all data</t>
@@ -1333,29 +1389,41 @@
     <t>How a resource reference is interpreted when testing consent restrictions.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-data-meaning|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/consent-data-meaning|5.0.0</t>
   </si>
   <si>
     <t>Consent.provision.data.reference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t>The actual data reference</t>
+  </si>
+  <si>
+    <t>A reference to a specific resource that defines which resources are covered by this consent.</t>
+  </si>
+  <si>
+    <t>Consent.provision.expression</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expression
 </t>
   </si>
   <si>
-    <t>The actual data reference</t>
-  </si>
-  <si>
-    <t>A reference to a specific resource that defines which resources are covered by this consent.</t>
+    <t>A computable expression of the consent</t>
+  </si>
+  <si>
+    <t>A computable (FHIRPath or other) definition of what is controlled by this consent.</t>
+  </si>
+  <si>
+    <t>Constraining the expression type for a specific implementation via profile is recommended</t>
   </si>
   <si>
     <t>Consent.provision.provision</t>
   </si>
   <si>
-    <t>Nested Exception Rules</t>
-  </si>
-  <si>
-    <t>Rules which provide exceptions to the base rule or subrules.</t>
+    <t>Nested Exception Provisions</t>
+  </si>
+  <si>
+    <t>Provisions which provide exceptions to the base provision or subprovisions.</t>
   </si>
 </sst>
 </file>
@@ -1489,7 +1557,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -1576,77 +1644,85 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="B13" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>22</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>26</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
         <v>35</v>
       </c>
-      <c r="B20" t="s" s="2">
+      <c r="B21" t="s" s="2">
         <v>36</v>
       </c>
     </row>
@@ -1657,7 +1733,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN84"/>
+  <dimension ref="A1:AN81"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="40.04296875" customWidth="true" bestFit="true"/>
@@ -1670,7 +1746,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="94.234375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="98.53515625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1679,7 +1755,7 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="42.44921875" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
@@ -1696,9 +1772,9 @@
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="46.4453125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="46.53125" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="62.40234375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="46.53125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1934,15 +2010,15 @@
         <v>86</v>
       </c>
       <c r="AN2" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1953,7 +2029,7 @@
         <v>78</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>77</v>
@@ -1962,19 +2038,19 @@
         <v>77</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2024,13 +2100,13 @@
         <v>77</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>77</v>
@@ -2053,10 +2129,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2067,7 +2143,7 @@
         <v>78</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>77</v>
@@ -2076,16 +2152,16 @@
         <v>77</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2136,19 +2212,19 @@
         <v>77</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>77</v>
@@ -2165,10 +2241,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2179,28 +2255,28 @@
         <v>78</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2250,19 +2326,19 @@
         <v>77</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>77</v>
@@ -2279,10 +2355,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2293,7 +2369,7 @@
         <v>78</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>77</v>
@@ -2305,16 +2381,16 @@
         <v>77</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2340,13 +2416,13 @@
         <v>77</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>77</v>
@@ -2364,19 +2440,19 @@
         <v>77</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>77</v>
@@ -2393,21 +2469,21 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>77</v>
@@ -2419,16 +2495,16 @@
         <v>77</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2478,19 +2554,19 @@
         <v>77</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>77</v>
+        <v>124</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>77</v>
@@ -2499,22 +2575,22 @@
         <v>77</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>123</v>
+        <v>77</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>77</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2533,16 +2609,16 @@
         <v>77</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2592,7 +2668,7 @@
         <v>77</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
@@ -2601,7 +2677,7 @@
         <v>79</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>77</v>
+        <v>133</v>
       </c>
       <c r="AJ8" t="s" s="2">
         <v>77</v>
@@ -2613,22 +2689,22 @@
         <v>77</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>77</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2647,16 +2723,16 @@
         <v>77</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2706,7 +2782,7 @@
         <v>77</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -2718,7 +2794,7 @@
         <v>77</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>77</v>
@@ -2727,22 +2803,22 @@
         <v>77</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>77</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2755,25 +2831,25 @@
         <v>77</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>77</v>
@@ -2822,7 +2898,7 @@
         <v>77</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2834,7 +2910,7 @@
         <v>77</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>77</v>
@@ -2843,18 +2919,18 @@
         <v>77</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>77</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2874,19 +2950,19 @@
         <v>77</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -2900,7 +2976,7 @@
         <v>77</v>
       </c>
       <c r="T11" t="s" s="2">
-        <v>150</v>
+        <v>77</v>
       </c>
       <c r="U11" t="s" s="2">
         <v>77</v>
@@ -2936,7 +3012,7 @@
         <v>77</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2948,27 +3024,27 @@
         <v>77</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>77</v>
+        <v>154</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>153</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2976,35 +3052,33 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="O12" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>77</v>
       </c>
@@ -3028,7 +3102,7 @@
         <v>77</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="Y12" t="s" s="2">
         <v>160</v>
@@ -3052,19 +3126,19 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>162</v>
@@ -3076,15 +3150,15 @@
         <v>164</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3092,28 +3166,28 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>168</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>169</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3140,52 +3214,52 @@
         <v>77</v>
       </c>
       <c r="X13" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="Y13" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="Y13" t="s" s="2">
+      <c r="Z13" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="Z13" t="s" s="2">
+      <c r="AA13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF13" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AG13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH13" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK13" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="AA13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="AG13" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH13" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ13" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK13" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="AL13" t="s" s="2">
-        <v>77</v>
+        <v>173</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>77</v>
+        <v>174</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>77</v>
@@ -3193,10 +3267,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3207,7 +3281,7 @@
         <v>78</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>77</v>
@@ -3219,13 +3293,13 @@
         <v>77</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>174</v>
+        <v>91</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3276,16 +3350,16 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>77</v>
+        <v>179</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>77</v>
@@ -3297,22 +3371,22 @@
         <v>77</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>77</v>
+        <v>180</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3331,16 +3405,16 @@
         <v>77</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3378,19 +3452,19 @@
         <v>77</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="AD15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3402,7 +3476,7 @@
         <v>77</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>77</v>
@@ -3411,18 +3485,18 @@
         <v>77</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>77</v>
+        <v>180</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3442,22 +3516,22 @@
         <v>77</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>77</v>
@@ -3506,7 +3580,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3518,27 +3592,27 @@
         <v>77</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>192</v>
+        <v>77</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>77</v>
+        <v>195</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3549,7 +3623,7 @@
         <v>78</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>77</v>
@@ -3561,13 +3635,13 @@
         <v>77</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>174</v>
+        <v>91</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3618,16 +3692,16 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>77</v>
+        <v>179</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>77</v>
@@ -3639,22 +3713,22 @@
         <v>77</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>77</v>
+        <v>180</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3673,16 +3747,16 @@
         <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3720,19 +3794,19 @@
         <v>77</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3744,7 +3818,7 @@
         <v>77</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>77</v>
@@ -3753,18 +3827,18 @@
         <v>77</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>77</v>
+        <v>180</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3775,7 +3849,7 @@
         <v>78</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>77</v>
@@ -3784,22 +3858,22 @@
         <v>77</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>77</v>
@@ -3809,7 +3883,7 @@
         <v>77</v>
       </c>
       <c r="S19" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="T19" t="s" s="2">
         <v>77</v>
@@ -3848,39 +3922,39 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>203</v>
+        <v>77</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>77</v>
+        <v>206</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3891,7 +3965,7 @@
         <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>77</v>
@@ -3900,19 +3974,19 @@
         <v>77</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>174</v>
+        <v>208</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3962,39 +4036,39 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>210</v>
+        <v>77</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>77</v>
+        <v>214</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4005,7 +4079,7 @@
         <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>77</v>
@@ -4014,20 +4088,20 @@
         <v>77</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>77</v>
@@ -4037,7 +4111,7 @@
         <v>77</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="T21" t="s" s="2">
         <v>77</v>
@@ -4076,39 +4150,39 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>77</v>
+        <v>221</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>218</v>
+        <v>77</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>77</v>
+        <v>223</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4119,7 +4193,7 @@
         <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>77</v>
@@ -4128,20 +4202,20 @@
         <v>77</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>174</v>
+        <v>208</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>77</v>
@@ -4190,39 +4264,39 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>77</v>
+        <v>221</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>225</v>
+        <v>77</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>77</v>
+        <v>230</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4233,7 +4307,7 @@
         <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>77</v>
@@ -4242,22 +4316,22 @@
         <v>77</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>77</v>
@@ -4306,39 +4380,39 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>234</v>
+        <v>77</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>77</v>
+        <v>239</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4349,7 +4423,7 @@
         <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>77</v>
@@ -4358,22 +4432,22 @@
         <v>77</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>174</v>
+        <v>208</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>77</v>
@@ -4422,39 +4496,39 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>242</v>
+        <v>77</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>77</v>
+        <v>247</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4462,10 +4536,10 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>77</v>
@@ -4474,16 +4548,16 @@
         <v>77</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>167</v>
+        <v>249</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4510,63 +4584,63 @@
         <v>77</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>170</v>
+        <v>77</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>247</v>
+        <v>77</v>
       </c>
       <c r="Z25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="AA25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>244</v>
-      </c>
       <c r="AG25" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>251</v>
+        <v>77</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>252</v>
+        <v>77</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4577,7 +4651,7 @@
         <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>77</v>
@@ -4586,16 +4660,16 @@
         <v>77</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>174</v>
+        <v>255</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>175</v>
+        <v>256</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>176</v>
+        <v>257</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4646,28 +4720,28 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>177</v>
+        <v>254</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>77</v>
+        <v>258</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>77</v>
+        <v>259</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>178</v>
+        <v>260</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>77</v>
@@ -4675,21 +4749,21 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>133</v>
+        <v>262</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>77</v>
@@ -4698,20 +4772,18 @@
         <v>77</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>134</v>
+        <v>263</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>135</v>
+        <v>264</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -4748,31 +4820,31 @@
         <v>77</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>181</v>
+        <v>77</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>182</v>
+        <v>77</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>183</v>
+        <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>184</v>
+        <v>261</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>139</v>
+        <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>77</v>
@@ -4781,7 +4853,7 @@
         <v>77</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>77</v>
@@ -4789,14 +4861,14 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>77</v>
+        <v>267</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4812,23 +4884,19 @@
         <v>77</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>186</v>
+        <v>268</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>187</v>
+        <v>269</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>190</v>
-      </c>
+        <v>270</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>77</v>
       </c>
@@ -4876,7 +4944,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>191</v>
+        <v>266</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4888,16 +4956,16 @@
         <v>77</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>192</v>
+        <v>77</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>193</v>
+        <v>77</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>77</v>
@@ -4905,21 +4973,21 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>256</v>
+        <v>271</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>256</v>
+        <v>271</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>77</v>
+        <v>272</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>77</v>
@@ -4928,18 +4996,20 @@
         <v>77</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>174</v>
+        <v>268</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>175</v>
+        <v>273</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>274</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>275</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>77</v>
@@ -4988,19 +5058,19 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>177</v>
+        <v>271</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>77</v>
@@ -5009,7 +5079,7 @@
         <v>77</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>77</v>
@@ -5017,14 +5087,14 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>257</v>
+        <v>276</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>257</v>
+        <v>276</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>133</v>
+        <v>277</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5043,17 +5113,15 @@
         <v>77</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>134</v>
+        <v>278</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>135</v>
+        <v>279</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>280</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>77</v>
@@ -5090,19 +5158,19 @@
         <v>77</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>181</v>
+        <v>77</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>182</v>
+        <v>77</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>183</v>
+        <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>184</v>
+        <v>276</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5114,16 +5182,16 @@
         <v>77</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>139</v>
+        <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>77</v>
+        <v>281</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>77</v>
@@ -5131,21 +5199,21 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>258</v>
+        <v>282</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>258</v>
+        <v>282</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>77</v>
+        <v>283</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>77</v>
@@ -5154,23 +5222,19 @@
         <v>77</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>102</v>
+        <v>278</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>197</v>
+        <v>284</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>200</v>
-      </c>
+        <v>285</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>77</v>
       </c>
@@ -5179,7 +5243,7 @@
         <v>77</v>
       </c>
       <c r="S31" t="s" s="2">
-        <v>259</v>
+        <v>77</v>
       </c>
       <c r="T31" t="s" s="2">
         <v>77</v>
@@ -5218,28 +5282,28 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>202</v>
+        <v>282</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>203</v>
+        <v>77</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>204</v>
+        <v>77</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>77</v>
@@ -5247,10 +5311,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>260</v>
+        <v>286</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>260</v>
+        <v>286</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5261,7 +5325,7 @@
         <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>77</v>
@@ -5270,19 +5334,19 @@
         <v>77</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>174</v>
+        <v>287</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>206</v>
+        <v>288</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>207</v>
+        <v>289</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>208</v>
+        <v>290</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5332,28 +5396,28 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>209</v>
+        <v>286</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>210</v>
+        <v>77</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>211</v>
+        <v>291</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>77</v>
@@ -5361,10 +5425,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5375,7 +5439,7 @@
         <v>78</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>77</v>
@@ -5384,21 +5448,21 @@
         <v>77</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>108</v>
+        <v>293</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>213</v>
+        <v>288</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="N33" s="2"/>
-      <c r="O33" t="s" s="2">
-        <v>215</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>77</v>
       </c>
@@ -5407,7 +5471,7 @@
         <v>77</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>262</v>
+        <v>77</v>
       </c>
       <c r="T33" t="s" s="2">
         <v>77</v>
@@ -5446,28 +5510,28 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>217</v>
+        <v>292</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>218</v>
+        <v>77</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>219</v>
+        <v>291</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>77</v>
@@ -5475,10 +5539,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>263</v>
+        <v>295</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>263</v>
+        <v>295</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5486,10 +5550,10 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>77</v>
@@ -5498,21 +5562,19 @@
         <v>77</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>221</v>
+        <v>296</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>222</v>
+        <v>297</v>
       </c>
       <c r="N34" s="2"/>
-      <c r="O34" t="s" s="2">
-        <v>223</v>
-      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>77</v>
       </c>
@@ -5536,13 +5598,11 @@
         <v>77</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y34" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
-        <v>77</v>
+        <v>298</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>77</v>
@@ -5560,28 +5620,28 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>224</v>
+        <v>295</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>225</v>
+        <v>77</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>226</v>
+        <v>299</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>77</v>
@@ -5589,10 +5649,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>264</v>
+        <v>300</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>264</v>
+        <v>300</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5603,7 +5663,7 @@
         <v>78</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>77</v>
@@ -5612,23 +5672,19 @@
         <v>77</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>228</v>
+        <v>91</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>229</v>
+        <v>176</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>232</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>77</v>
       </c>
@@ -5676,50 +5732,50 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>233</v>
+        <v>178</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>77</v>
+        <v>179</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>234</v>
+        <v>77</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>235</v>
+        <v>77</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>77</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>265</v>
+        <v>301</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>265</v>
+        <v>301</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>77</v>
@@ -5728,23 +5784,21 @@
         <v>77</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>174</v>
+        <v>137</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>237</v>
+        <v>138</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>238</v>
+        <v>182</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>240</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>77</v>
       </c>
@@ -5780,51 +5834,51 @@
         <v>77</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>77</v>
+        <v>183</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>77</v>
+        <v>184</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>77</v>
+        <v>185</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>241</v>
+        <v>186</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>100</v>
+        <v>142</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>242</v>
+        <v>77</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>243</v>
+        <v>77</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>77</v>
+        <v>180</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>266</v>
+        <v>302</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>266</v>
+        <v>302</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5832,10 +5886,10 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>77</v>
@@ -5844,21 +5898,23 @@
         <v>77</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>267</v>
+        <v>188</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>268</v>
+        <v>189</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>269</v>
+        <v>190</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="O37" s="2"/>
+        <v>191</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>192</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>77</v>
       </c>
@@ -5906,39 +5962,39 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>266</v>
+        <v>193</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>271</v>
+        <v>77</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>272</v>
+        <v>194</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>273</v>
+        <v>195</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>274</v>
+        <v>303</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>274</v>
+        <v>303</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5949,7 +6005,7 @@
         <v>78</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>77</v>
@@ -5958,21 +6014,23 @@
         <v>77</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>275</v>
+        <v>208</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>276</v>
+        <v>241</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>277</v>
+        <v>242</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="O38" s="2"/>
+        <v>243</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>244</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>77</v>
       </c>
@@ -5981,7 +6039,7 @@
         <v>77</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>77</v>
+        <v>304</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>77</v>
@@ -6020,50 +6078,50 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>274</v>
+        <v>245</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>279</v>
+        <v>77</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>280</v>
+        <v>77</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>281</v>
+        <v>246</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>282</v>
+        <v>247</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>283</v>
+        <v>305</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>283</v>
+        <v>305</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>284</v>
+        <v>77</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>77</v>
@@ -6072,20 +6130,18 @@
         <v>77</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>285</v>
+        <v>306</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>288</v>
-      </c>
+        <v>308</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>77</v>
@@ -6134,50 +6190,50 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>283</v>
+        <v>305</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>289</v>
+        <v>77</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>290</v>
+        <v>77</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>291</v>
+        <v>77</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>292</v>
+        <v>309</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>292</v>
+        <v>309</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>293</v>
+        <v>77</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>77</v>
@@ -6186,16 +6242,16 @@
         <v>77</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>294</v>
+        <v>208</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>295</v>
+        <v>176</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>296</v>
+        <v>177</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6246,22 +6302,22 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>292</v>
+        <v>178</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>77</v>
+        <v>179</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>289</v>
+        <v>77</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>77</v>
@@ -6270,26 +6326,26 @@
         <v>77</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>297</v>
+        <v>180</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>77</v>
@@ -6298,19 +6354,19 @@
         <v>77</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>299</v>
+        <v>137</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>300</v>
+        <v>138</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>301</v>
+        <v>182</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>302</v>
+        <v>140</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6360,43 +6416,43 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>298</v>
+        <v>186</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>100</v>
+        <v>142</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>303</v>
+        <v>77</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>77</v>
+        <v>180</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>77</v>
+        <v>312</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6409,22 +6465,26 @@
         <v>77</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>305</v>
+        <v>137</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
+        <v>314</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>77</v>
       </c>
@@ -6472,7 +6532,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6484,7 +6544,7 @@
         <v>77</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>100</v>
+        <v>142</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>77</v>
@@ -6496,15 +6556,15 @@
         <v>77</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>77</v>
+        <v>134</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6515,7 +6575,7 @@
         <v>78</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>77</v>
@@ -6527,15 +6587,17 @@
         <v>77</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>174</v>
+        <v>317</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>175</v>
+        <v>318</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>319</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>320</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>77</v>
@@ -6584,19 +6646,19 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>177</v>
+        <v>316</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>77</v>
@@ -6605,7 +6667,7 @@
         <v>77</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>77</v>
@@ -6613,21 +6675,21 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>133</v>
+        <v>77</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>77</v>
@@ -6639,17 +6701,15 @@
         <v>77</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>134</v>
+        <v>322</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>135</v>
+        <v>323</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>77</v>
@@ -6698,19 +6758,19 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>184</v>
+        <v>321</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>139</v>
+        <v>101</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>77</v>
@@ -6719,7 +6779,7 @@
         <v>77</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>77</v>
@@ -6727,14 +6787,14 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>311</v>
+        <v>77</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6747,26 +6807,22 @@
         <v>77</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>134</v>
+        <v>326</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>312</v>
+        <v>327</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>328</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>77</v>
       </c>
@@ -6814,7 +6870,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6826,7 +6882,7 @@
         <v>77</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>139</v>
+        <v>101</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>77</v>
@@ -6835,7 +6891,7 @@
         <v>77</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>77</v>
@@ -6843,10 +6899,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>315</v>
+        <v>329</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>315</v>
+        <v>329</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6857,7 +6913,7 @@
         <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>77</v>
@@ -6866,16 +6922,16 @@
         <v>77</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>102</v>
+        <v>306</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>317</v>
+        <v>331</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6926,19 +6982,19 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>315</v>
+        <v>329</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>318</v>
+        <v>77</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>77</v>
@@ -6955,10 +7011,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>319</v>
+        <v>332</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>319</v>
+        <v>332</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6969,7 +7025,7 @@
         <v>78</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>77</v>
@@ -6981,17 +7037,15 @@
         <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>102</v>
+        <v>208</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>320</v>
+        <v>176</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>321</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>77</v>
@@ -7040,19 +7094,19 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>319</v>
+        <v>178</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>318</v>
+        <v>179</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>77</v>
@@ -7064,26 +7118,26 @@
         <v>77</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>77</v>
+        <v>180</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>77</v>
@@ -7092,23 +7146,21 @@
         <v>77</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>323</v>
+        <v>138</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>324</v>
+        <v>182</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>326</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>77</v>
       </c>
@@ -7132,11 +7184,13 @@
         <v>77</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="Y48" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z48" t="s" s="2">
-        <v>327</v>
+        <v>77</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>77</v>
@@ -7154,19 +7208,19 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>322</v>
+        <v>186</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>318</v>
+        <v>77</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>100</v>
+        <v>142</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>77</v>
@@ -7178,47 +7232,51 @@
         <v>77</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>77</v>
+        <v>180</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>77</v>
+        <v>312</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>174</v>
+        <v>137</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>175</v>
+        <v>313</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
+        <v>314</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>77</v>
       </c>
@@ -7266,19 +7324,19 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>177</v>
+        <v>315</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>77</v>
+        <v>142</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>77</v>
@@ -7287,29 +7345,29 @@
         <v>77</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>77</v>
+        <v>134</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>133</v>
+        <v>77</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>77</v>
@@ -7318,20 +7376,18 @@
         <v>77</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>134</v>
+        <v>232</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>135</v>
+        <v>336</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>337</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>77</v>
@@ -7368,31 +7424,31 @@
         <v>77</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>181</v>
+        <v>77</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>182</v>
+        <v>77</v>
       </c>
       <c r="AD50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>183</v>
+        <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>184</v>
+        <v>335</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>139</v>
+        <v>101</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>77</v>
@@ -7401,7 +7457,7 @@
         <v>77</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>77</v>
@@ -7409,10 +7465,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7423,7 +7479,7 @@
         <v>78</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>77</v>
@@ -7432,23 +7488,21 @@
         <v>77</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>187</v>
+        <v>339</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>188</v>
+        <v>340</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>190</v>
-      </c>
+        <v>341</v>
+      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>77</v>
       </c>
@@ -7472,13 +7526,13 @@
         <v>77</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>77</v>
+        <v>169</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>77</v>
+        <v>342</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>77</v>
+        <v>343</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>77</v>
@@ -7496,28 +7550,28 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>191</v>
+        <v>338</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>192</v>
+        <v>77</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>193</v>
+        <v>77</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>77</v>
@@ -7525,10 +7579,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>331</v>
+        <v>344</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>331</v>
+        <v>344</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7539,7 +7593,7 @@
         <v>78</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>77</v>
@@ -7548,23 +7602,19 @@
         <v>77</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>174</v>
+        <v>345</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>237</v>
+        <v>346</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>240</v>
-      </c>
+        <v>347</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>77</v>
       </c>
@@ -7573,7 +7623,7 @@
         <v>77</v>
       </c>
       <c r="S52" t="s" s="2">
-        <v>332</v>
+        <v>77</v>
       </c>
       <c r="T52" t="s" s="2">
         <v>77</v>
@@ -7612,28 +7662,28 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>241</v>
+        <v>344</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>242</v>
+        <v>77</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>243</v>
+        <v>77</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>77</v>
@@ -7641,10 +7691,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>333</v>
+        <v>348</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>333</v>
+        <v>348</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7655,7 +7705,7 @@
         <v>78</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>77</v>
@@ -7664,16 +7714,16 @@
         <v>77</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>305</v>
+        <v>349</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>334</v>
+        <v>350</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>335</v>
+        <v>351</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7724,19 +7774,19 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>333</v>
+        <v>348</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>77</v>
@@ -7753,10 +7803,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>336</v>
+        <v>352</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>336</v>
+        <v>352</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7767,7 +7817,7 @@
         <v>78</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>77</v>
@@ -7779,15 +7829,17 @@
         <v>77</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>174</v>
+        <v>353</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>175</v>
+        <v>354</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>355</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>356</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>77</v>
@@ -7836,19 +7888,19 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>177</v>
+        <v>352</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>77</v>
@@ -7857,7 +7909,7 @@
         <v>77</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>77</v>
@@ -7865,43 +7917,41 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>337</v>
+        <v>357</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>337</v>
+        <v>357</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>133</v>
+        <v>77</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>135</v>
+        <v>358</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>359</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>77</v>
@@ -7926,13 +7976,13 @@
         <v>77</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>77</v>
+        <v>360</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>77</v>
+        <v>361</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>77</v>
@@ -7950,19 +8000,19 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>184</v>
+        <v>357</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>139</v>
+        <v>101</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>77</v>
@@ -7971,7 +8021,7 @@
         <v>77</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>77</v>
@@ -7979,14 +8029,14 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>338</v>
+        <v>362</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>338</v>
+        <v>362</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>311</v>
+        <v>77</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -7999,26 +8049,22 @@
         <v>77</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>134</v>
+        <v>306</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>312</v>
+        <v>363</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>77</v>
       </c>
@@ -8066,7 +8112,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>314</v>
+        <v>362</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8078,7 +8124,7 @@
         <v>77</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>139</v>
+        <v>101</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>77</v>
@@ -8087,7 +8133,7 @@
         <v>77</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>77</v>
@@ -8095,10 +8141,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>339</v>
+        <v>365</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>339</v>
+        <v>365</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8106,10 +8152,10 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>77</v>
@@ -8118,16 +8164,16 @@
         <v>77</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>228</v>
+        <v>208</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>340</v>
+        <v>176</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>341</v>
+        <v>177</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8178,19 +8224,19 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>339</v>
+        <v>178</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>77</v>
+        <v>179</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>77</v>
@@ -8202,26 +8248,26 @@
         <v>77</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>77</v>
+        <v>180</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>342</v>
+        <v>366</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>342</v>
+        <v>366</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>77</v>
@@ -8233,15 +8279,17 @@
         <v>77</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>343</v>
+        <v>137</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>344</v>
+        <v>138</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>182</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>77</v>
@@ -8290,19 +8338,19 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>342</v>
+        <v>186</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>100</v>
+        <v>142</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>77</v>
@@ -8314,47 +8362,51 @@
         <v>77</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>77</v>
+        <v>180</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>346</v>
+        <v>367</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>346</v>
+        <v>367</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>77</v>
+        <v>312</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>275</v>
+        <v>137</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>347</v>
+        <v>313</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
+        <v>314</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>77</v>
       </c>
@@ -8402,19 +8454,19 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>346</v>
+        <v>315</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>100</v>
+        <v>142</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>77</v>
@@ -8426,15 +8478,15 @@
         <v>77</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>77</v>
+        <v>134</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>349</v>
+        <v>368</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>349</v>
+        <v>368</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8442,10 +8494,10 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>77</v>
@@ -8454,18 +8506,20 @@
         <v>77</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>305</v>
+        <v>263</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>350</v>
+        <v>369</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="N60" s="2"/>
+        <v>370</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>371</v>
+      </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>77</v>
@@ -8514,19 +8568,19 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>349</v>
+        <v>368</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>77</v>
@@ -8535,7 +8589,7 @@
         <v>77</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>77</v>
+        <v>372</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>77</v>
@@ -8543,10 +8597,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>352</v>
+        <v>373</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>352</v>
+        <v>373</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8557,7 +8611,7 @@
         <v>78</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>77</v>
@@ -8569,20 +8623,22 @@
         <v>77</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>174</v>
+        <v>306</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>175</v>
+        <v>374</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>176</v>
+        <v>375</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q61" s="2"/>
+      <c r="Q61" t="s" s="2">
+        <v>376</v>
+      </c>
       <c r="R61" t="s" s="2">
         <v>77</v>
       </c>
@@ -8626,19 +8682,19 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>177</v>
+        <v>373</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>77</v>
@@ -8647,7 +8703,7 @@
         <v>77</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>77</v>
@@ -8655,21 +8711,21 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>353</v>
+        <v>377</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>353</v>
+        <v>377</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>133</v>
+        <v>77</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>77</v>
@@ -8681,17 +8737,15 @@
         <v>77</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>134</v>
+        <v>208</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>135</v>
+        <v>176</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="N62" s="2"/>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>77</v>
@@ -8740,19 +8794,19 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>77</v>
+        <v>179</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>77</v>
@@ -8761,22 +8815,22 @@
         <v>77</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>77</v>
+        <v>180</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>354</v>
+        <v>378</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>354</v>
+        <v>378</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>311</v>
+        <v>136</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -8789,26 +8843,24 @@
         <v>77</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>312</v>
+        <v>138</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>313</v>
+        <v>182</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>77</v>
       </c>
@@ -8856,7 +8908,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>314</v>
+        <v>186</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -8868,7 +8920,7 @@
         <v>77</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>77</v>
@@ -8877,50 +8929,54 @@
         <v>77</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>77</v>
+        <v>180</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>355</v>
+        <v>379</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>355</v>
+        <v>379</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>77</v>
+        <v>312</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>356</v>
+        <v>313</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="N64" s="2"/>
-      <c r="O64" s="2"/>
+        <v>314</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>77</v>
       </c>
@@ -8944,13 +9000,13 @@
         <v>77</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>159</v>
+        <v>77</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>358</v>
+        <v>77</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>359</v>
+        <v>77</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>77</v>
@@ -8968,19 +9024,19 @@
         <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>355</v>
+        <v>315</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>100</v>
+        <v>142</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>77</v>
@@ -8992,15 +9048,15 @@
         <v>77</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>77</v>
+        <v>134</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9011,7 +9067,7 @@
         <v>78</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>77</v>
@@ -9020,16 +9076,16 @@
         <v>77</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>361</v>
+        <v>166</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>362</v>
+        <v>381</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>363</v>
+        <v>382</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9056,13 +9112,13 @@
         <v>77</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>77</v>
+        <v>383</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>77</v>
+        <v>384</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>77</v>
+        <v>385</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>77</v>
@@ -9080,19 +9136,19 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>77</v>
@@ -9109,10 +9165,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>364</v>
+        <v>386</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>364</v>
+        <v>386</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9123,7 +9179,7 @@
         <v>78</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>77</v>
@@ -9135,22 +9191,20 @@
         <v>77</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>305</v>
+        <v>387</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>365</v>
+        <v>388</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>366</v>
+        <v>389</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q66" t="s" s="2">
-        <v>367</v>
-      </c>
+      <c r="Q66" s="2"/>
       <c r="R66" t="s" s="2">
         <v>77</v>
       </c>
@@ -9194,19 +9248,19 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>364</v>
+        <v>386</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>77</v>
@@ -9223,10 +9277,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>368</v>
+        <v>390</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>368</v>
+        <v>390</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9237,7 +9291,7 @@
         <v>78</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>77</v>
@@ -9246,23 +9300,27 @@
         <v>77</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>175</v>
+        <v>391</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N67" s="2"/>
+        <v>392</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>393</v>
+      </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q67" s="2"/>
+      <c r="Q67" t="s" s="2">
+        <v>394</v>
+      </c>
       <c r="R67" t="s" s="2">
         <v>77</v>
       </c>
@@ -9282,13 +9340,13 @@
         <v>77</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>77</v>
+        <v>169</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>77</v>
+        <v>395</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>77</v>
+        <v>396</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>77</v>
@@ -9306,19 +9364,19 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>177</v>
+        <v>390</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>77</v>
@@ -9327,7 +9385,7 @@
         <v>77</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>77</v>
@@ -9335,14 +9393,14 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>369</v>
+        <v>397</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>369</v>
+        <v>397</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>133</v>
+        <v>77</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -9358,19 +9416,19 @@
         <v>77</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>134</v>
+        <v>188</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>135</v>
+        <v>398</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>180</v>
+        <v>399</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>137</v>
+        <v>400</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -9396,13 +9454,13 @@
         <v>77</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>77</v>
+        <v>169</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>77</v>
+        <v>401</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>77</v>
+        <v>402</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>77</v>
@@ -9420,7 +9478,7 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>184</v>
+        <v>397</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -9432,7 +9490,7 @@
         <v>77</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>139</v>
+        <v>101</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>77</v>
@@ -9441,7 +9499,7 @@
         <v>77</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>77</v>
@@ -9449,14 +9507,14 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>370</v>
+        <v>403</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>370</v>
+        <v>403</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>311</v>
+        <v>77</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -9469,26 +9527,24 @@
         <v>77</v>
       </c>
       <c r="I69" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>134</v>
+        <v>188</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>312</v>
+        <v>404</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>313</v>
+        <v>405</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>406</v>
+      </c>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>77</v>
       </c>
@@ -9512,13 +9568,13 @@
         <v>77</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>77</v>
+        <v>383</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>77</v>
+        <v>407</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>77</v>
+        <v>408</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>77</v>
@@ -9536,7 +9592,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>314</v>
+        <v>403</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -9548,7 +9604,7 @@
         <v>77</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>139</v>
+        <v>101</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>77</v>
@@ -9557,7 +9613,7 @@
         <v>77</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>77</v>
@@ -9565,10 +9621,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>371</v>
+        <v>409</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>371</v>
+        <v>409</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9576,10 +9632,10 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>77</v>
@@ -9588,18 +9644,20 @@
         <v>77</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>167</v>
+        <v>188</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>372</v>
+        <v>410</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="N70" s="2"/>
+        <v>411</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>412</v>
+      </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>77</v>
@@ -9624,13 +9682,13 @@
         <v>77</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>170</v>
+        <v>413</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>374</v>
+        <v>414</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>375</v>
+        <v>415</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>77</v>
@@ -9648,19 +9706,19 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>371</v>
+        <v>409</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>77</v>
@@ -9677,10 +9735,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>376</v>
+        <v>416</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>376</v>
+        <v>416</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9688,10 +9746,10 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>77</v>
@@ -9700,18 +9758,20 @@
         <v>77</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>377</v>
+        <v>188</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>378</v>
+        <v>417</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="N71" s="2"/>
+        <v>418</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>419</v>
+      </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>77</v>
@@ -9736,13 +9796,13 @@
         <v>77</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>77</v>
+        <v>383</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>77</v>
+        <v>420</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>77</v>
+        <v>421</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>77</v>
@@ -9760,19 +9820,19 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>376</v>
+        <v>416</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>77</v>
@@ -9789,10 +9849,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>380</v>
+        <v>422</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>380</v>
+        <v>422</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9812,27 +9872,23 @@
         <v>77</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>381</v>
+        <v>423</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>383</v>
-      </c>
+        <v>424</v>
+      </c>
+      <c r="N72" s="2"/>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q72" t="s" s="2">
-        <v>384</v>
-      </c>
+      <c r="Q72" s="2"/>
       <c r="R72" t="s" s="2">
         <v>77</v>
       </c>
@@ -9852,13 +9908,13 @@
         <v>77</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>385</v>
+        <v>169</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>386</v>
+        <v>425</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>387</v>
+        <v>426</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>77</v>
@@ -9876,7 +9932,7 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>380</v>
+        <v>422</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -9888,7 +9944,7 @@
         <v>77</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>77</v>
@@ -9905,10 +9961,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>388</v>
+        <v>427</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>388</v>
+        <v>427</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9919,7 +9975,7 @@
         <v>78</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>77</v>
@@ -9928,19 +9984,19 @@
         <v>77</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>186</v>
+        <v>263</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>389</v>
+        <v>428</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>390</v>
+        <v>429</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>391</v>
+        <v>430</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -9966,13 +10022,13 @@
         <v>77</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>170</v>
+        <v>77</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>392</v>
+        <v>77</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>393</v>
+        <v>77</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>77</v>
@@ -9990,19 +10046,19 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>388</v>
+        <v>427</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>77</v>
@@ -10019,10 +10075,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>394</v>
+        <v>431</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>394</v>
+        <v>431</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10042,25 +10098,25 @@
         <v>77</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>186</v>
+        <v>306</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>395</v>
+        <v>432</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>397</v>
-      </c>
+        <v>433</v>
+      </c>
+      <c r="N74" s="2"/>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q74" s="2"/>
+      <c r="Q74" t="s" s="2">
+        <v>434</v>
+      </c>
       <c r="R74" t="s" s="2">
         <v>77</v>
       </c>
@@ -10080,13 +10136,13 @@
         <v>77</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>170</v>
+        <v>77</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>398</v>
+        <v>77</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>399</v>
+        <v>77</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>77</v>
@@ -10104,7 +10160,7 @@
         <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>394</v>
+        <v>431</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10116,7 +10172,7 @@
         <v>77</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>77</v>
@@ -10133,10 +10189,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>400</v>
+        <v>435</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>400</v>
+        <v>435</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10147,7 +10203,7 @@
         <v>78</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>77</v>
@@ -10156,20 +10212,18 @@
         <v>77</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>186</v>
+        <v>208</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>401</v>
+        <v>176</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>403</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="N75" s="2"/>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>77</v>
@@ -10194,13 +10248,13 @@
         <v>77</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>170</v>
+        <v>77</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>404</v>
+        <v>77</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>405</v>
+        <v>77</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>77</v>
@@ -10218,19 +10272,19 @@
         <v>77</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>400</v>
+        <v>178</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>77</v>
+        <v>179</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>77</v>
@@ -10242,19 +10296,19 @@
         <v>77</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>77</v>
+        <v>180</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>406</v>
+        <v>436</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>406</v>
+        <v>436</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -10270,19 +10324,19 @@
         <v>77</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>407</v>
+        <v>138</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>408</v>
+        <v>182</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>409</v>
+        <v>140</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -10308,13 +10362,13 @@
         <v>77</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>385</v>
+        <v>77</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>410</v>
+        <v>77</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>411</v>
+        <v>77</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>77</v>
@@ -10332,7 +10386,7 @@
         <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>406</v>
+        <v>186</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -10344,7 +10398,7 @@
         <v>77</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>100</v>
+        <v>142</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>77</v>
@@ -10356,49 +10410,51 @@
         <v>77</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>77</v>
+        <v>180</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>412</v>
+        <v>437</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>412</v>
+        <v>437</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>77</v>
+        <v>312</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I77" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>361</v>
+        <v>137</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>413</v>
+        <v>313</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>414</v>
+        <v>314</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="O77" s="2"/>
+        <v>140</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="P77" t="s" s="2">
         <v>77</v>
       </c>
@@ -10446,19 +10502,19 @@
         <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>412</v>
+        <v>315</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>100</v>
+        <v>142</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>77</v>
@@ -10470,15 +10526,15 @@
         <v>77</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>77</v>
+        <v>134</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>416</v>
+        <v>438</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>416</v>
+        <v>438</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10486,10 +10542,10 @@
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>77</v>
@@ -10498,25 +10554,23 @@
         <v>77</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>305</v>
+        <v>109</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>417</v>
+        <v>439</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>418</v>
+        <v>440</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q78" t="s" s="2">
-        <v>419</v>
-      </c>
+      <c r="Q78" s="2"/>
       <c r="R78" t="s" s="2">
         <v>77</v>
       </c>
@@ -10536,13 +10590,13 @@
         <v>77</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>77</v>
+        <v>441</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>77</v>
+        <v>442</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>77</v>
@@ -10560,19 +10614,19 @@
         <v>77</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>416</v>
+        <v>438</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>77</v>
@@ -10581,7 +10635,7 @@
         <v>77</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>272</v>
+        <v>77</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>77</v>
@@ -10589,10 +10643,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>420</v>
+        <v>443</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>420</v>
+        <v>443</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10600,10 +10654,10 @@
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>77</v>
@@ -10612,16 +10666,16 @@
         <v>77</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>174</v>
+        <v>317</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>175</v>
+        <v>444</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>176</v>
+        <v>445</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -10672,19 +10726,19 @@
         <v>77</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>177</v>
+        <v>443</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>77</v>
@@ -10693,7 +10747,7 @@
         <v>77</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>77</v>
@@ -10701,21 +10755,21 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>421</v>
+        <v>446</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>421</v>
+        <v>446</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>133</v>
+        <v>77</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>77</v>
@@ -10727,16 +10781,16 @@
         <v>77</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>134</v>
+        <v>447</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>135</v>
+        <v>448</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>180</v>
+        <v>449</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>137</v>
+        <v>450</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -10786,19 +10840,19 @@
         <v>77</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>184</v>
+        <v>446</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>139</v>
+        <v>101</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>77</v>
@@ -10807,7 +10861,7 @@
         <v>77</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>77</v>
@@ -10815,14 +10869,14 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>422</v>
+        <v>451</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>422</v>
+        <v>451</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>311</v>
+        <v>77</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -10835,26 +10889,22 @@
         <v>77</v>
       </c>
       <c r="I81" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>312</v>
+        <v>452</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>453</v>
+      </c>
+      <c r="N81" s="2"/>
+      <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>77</v>
       </c>
@@ -10902,7 +10952,7 @@
         <v>77</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>314</v>
+        <v>451</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -10914,7 +10964,7 @@
         <v>77</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>139</v>
+        <v>101</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>77</v>
@@ -10923,345 +10973,9 @@
         <v>77</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="B82" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="C82" s="2"/>
-      <c r="D82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E82" s="2"/>
-      <c r="F82" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="G82" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J82" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K82" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="L82" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="N82" s="2"/>
-      <c r="O82" s="2"/>
-      <c r="P82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q82" s="2"/>
-      <c r="R82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X82" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="Y82" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="Z82" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="AA82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF82" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="AG82" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH82" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ82" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="B83" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="C83" s="2"/>
-      <c r="D83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E83" s="2"/>
-      <c r="F83" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="G83" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J83" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K83" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="L83" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="N83" s="2"/>
-      <c r="O83" s="2"/>
-      <c r="P83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q83" s="2"/>
-      <c r="R83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF83" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="AG83" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH83" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ83" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="B84" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="C84" s="2"/>
-      <c r="D84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E84" s="2"/>
-      <c r="F84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="L84" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="N84" s="2"/>
-      <c r="O84" s="2"/>
-      <c r="P84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q84" s="2"/>
-      <c r="R84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF84" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="AG84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ84" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN84" t="s" s="2">
         <v>77</v>
       </c>
     </row>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T08:50:20+00:00</t>
+    <t>2023-05-10T08:50:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T08:50:38+00:00</t>
+    <t>2023-05-10T09:16:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T09:16:32+00:00</t>
+    <t>2023-05-10T09:16:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T09:16:57+00:00</t>
+    <t>2023-05-10T09:45:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T09:45:15+00:00</t>
+    <t>2023-05-10T09:50:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T09:50:54+00:00</t>
+    <t>2023-05-10T10:15:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T10:15:35+00:00</t>
+    <t>2023-05-10T10:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T10:16:16+00:00</t>
+    <t>2023-05-10T11:05:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T11:05:21+00:00</t>
+    <t>2023-05-10T11:05:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T11:05:55+00:00</t>
+    <t>2023-05-10T11:27:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T11:27:56+00:00</t>
+    <t>2023-05-10T11:35:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T11:35:39+00:00</t>
+    <t>2023-05-10T12:21:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T12:21:05+00:00</t>
+    <t>2023-05-10T12:21:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T12:21:34+00:00</t>
+    <t>2023-05-11T06:47:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T06:47:47+00:00</t>
+    <t>2023-05-11T06:48:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T06:48:00+00:00</t>
+    <t>2023-05-11T06:54:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T06:54:20+00:00</t>
+    <t>2023-05-11T06:54:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T06:54:25+00:00</t>
+    <t>2023-05-11T08:35:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T08:35:45+00:00</t>
+    <t>2023-05-11T08:41:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T08:41:43+00:00</t>
+    <t>2023-05-11T09:08:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T09:08:26+00:00</t>
+    <t>2023-05-11T09:17:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T09:17:12+00:00</t>
+    <t>2023-05-11T10:17:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:17:25+00:00</t>
+    <t>2023-05-11T10:17:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:17:56+00:00</t>
+    <t>2023-05-11T10:34:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:34:10+00:00</t>
+    <t>2023-05-11T10:41:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:41:58+00:00</t>
+    <t>2023-05-11T10:56:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:56:16+00:00</t>
+    <t>2023-05-11T10:56:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:56:44+00:00</t>
+    <t>2023-05-11T11:14:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T11:14:34+00:00</t>
+    <t>2023-05-11T11:21:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/StructureDefinition/receive-sms-messages</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv.json/StructureDefinition/receive-sms-messages</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T11:21:30+00:00</t>
+    <t>2023-05-11T11:55:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -946,7 +946,7 @@
     <t>A set of codes that indicate the regulatory basis (if any) that this consent supports.</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ValueSet/vs-patient-consent-for-sms-notifications</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv.json/ValueSet/vs-patient-consent-for-sms-notifications</t>
   </si>
   <si>
     <t>CON-3 (Consent Form ID and Version – ST)
@@ -1761,7 +1761,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="125.95703125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="78.23828125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="125.51953125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T11:55:17+00:00</t>
+    <t>2023-05-11T12:03:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv.json/StructureDefinition/receive-sms-messages</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/StructureDefinition/receive-sms-messages</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:03:20+00:00</t>
+    <t>2023-05-11T12:08:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -946,7 +946,7 @@
     <t>A set of codes that indicate the regulatory basis (if any) that this consent supports.</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv.json/ValueSet/vs-patient-consent-for-sms-notifications</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ValueSet/vs-patient-consent-for-sms-notifications</t>
   </si>
   <si>
     <t>CON-3 (Consent Form ID and Version – ST)
@@ -1761,7 +1761,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="125.95703125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="125.51953125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="78.23828125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:08:48+00:00</t>
+    <t>2023-05-11T12:16:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:16:35+00:00</t>
+    <t>2023-05-11T12:20:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:20:22+00:00</t>
+    <t>2023-05-11T12:21:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:21:18+00:00</t>
+    <t>2023-05-11T15:25:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T15:25:42+00:00</t>
+    <t>2023-05-11T15:26:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T15:26:02+00:00</t>
+    <t>2023-05-11T16:43:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T16:43:02+00:00</t>
+    <t>2023-05-11T16:43:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T16:43:55+00:00</t>
+    <t>2023-05-11T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T16:57:46+00:00</t>
+    <t>2023-05-11T16:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T16:58:30+00:00</t>
+    <t>2023-05-11T17:51:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T17:51:02+00:00</t>
+    <t>2023-05-11T17:51:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/StructureDefinition/receive-sms-messages</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv/StructureDefinition/receive-sms-messages</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T17:51:30+00:00</t>
+    <t>2023-05-11T18:15:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -946,7 +946,7 @@
     <t>A set of codes that indicate the regulatory basis (if any) that this consent supports.</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ValueSet/vs-patient-consent-for-sms-notifications</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv/ValueSet/vs-patient-consent-for-sms-notifications</t>
   </si>
   <si>
     <t>CON-3 (Consent Form ID and Version – ST)
@@ -1761,7 +1761,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="125.95703125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="78.23828125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="121.19140625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:15:51+00:00</t>
+    <t>2023-05-11T18:16:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv/StructureDefinition/receive-sms-messages</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/StructureDefinition/receive-sms-messages</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:16:31+00:00</t>
+    <t>2023-05-11T18:27:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -946,7 +946,7 @@
     <t>A set of codes that indicate the regulatory basis (if any) that this consent supports.</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv/ValueSet/vs-patient-consent-for-sms-notifications</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ValueSet/vs-patient-consent-for-sms-notifications</t>
   </si>
   <si>
     <t>CON-3 (Consent Form ID and Version – ST)
@@ -1761,7 +1761,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="125.95703125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="121.19140625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="78.23828125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:27:59+00:00</t>
+    <t>2023-05-11T18:29:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:29:46+00:00</t>
+    <t>2023-05-11T18:48:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:48:31+00:00</t>
+    <t>2023-05-11T18:54:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:54:41+00:00</t>
+    <t>2023-05-11T19:41:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:41:30+00:00</t>
+    <t>2023-05-11T19:42:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:42:15+00:00</t>
+    <t>2023-05-11T20:23:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T20:23:29+00:00</t>
+    <t>2023-05-11T20:24:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T20:24:51+00:00</t>
+    <t>2023-05-12T02:48:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T02:48:54+00:00</t>
+    <t>2023-05-12T02:49:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T02:49:37+00:00</t>
+    <t>2023-05-12T07:30:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:30:25+00:00</t>
+    <t>2023-05-12T07:30:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:30:35+00:00</t>
+    <t>2023-05-12T07:36:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:36:14+00:00</t>
+    <t>2023-05-12T07:36:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:36:30+00:00</t>
+    <t>2023-05-12T07:54:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:54:06+00:00</t>
+    <t>2023-05-12T07:55:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2939" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2542" uniqueCount="410">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:55:51+00:00</t>
+    <t>2023-05-12T10:26:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -541,6 +541,14 @@
     <t>A classification of the type of consents found in the statement. This element supports indexing and retrieval of consent statements.</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://loinc.org"/&gt;
+    &lt;code value="89057-4"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>example</t>
   </si>
   <si>
@@ -625,446 +633,310 @@
     <t>union(., ./translation)</t>
   </si>
   <si>
-    <t>Consent.category.coding.id</t>
-  </si>
-  <si>
-    <t>Consent.category.coding.extension</t>
-  </si>
-  <si>
-    <t>Consent.category.coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should be an absolute reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>http://loinc.org</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>Consent.category.coding.version</t>
+    <t>Consent.category.text</t>
   </si>
   <si>
     <t xml:space="preserve">string
 </t>
   </si>
   <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>Consent.category.coding.code</t>
-  </si>
-  <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>59284-0</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cod-1
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>Patient consent for SMS messages</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>Consent.subject</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Patient)
 </t>
   </si>
   <si>
-    <t>C*E.1</t>
-  </si>
-  <si>
-    <t>./code</t>
-  </si>
-  <si>
-    <t>Consent.category.coding.display</t>
-  </si>
-  <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>C*E.2 - but note this is not well followed</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>Consent.category.coding.userSelected</t>
+    <t>Who the consent applies to</t>
+  </si>
+  <si>
+    <t>The patient/healthcare practitioner or group of persons to whom this consent applies.</t>
+  </si>
+  <si>
+    <t>Event.subject</t>
+  </si>
+  <si>
+    <t>FiveWs.subject[x]</t>
+  </si>
+  <si>
+    <t>Consent.date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">date
+</t>
+  </si>
+  <si>
+    <t>Fully executed date of the consent</t>
+  </si>
+  <si>
+    <t>Date the consent instance was agreed to.</t>
+  </si>
+  <si>
+    <t>Event.occurrence[x]</t>
+  </si>
+  <si>
+    <t>FiveWs.recorded</t>
+  </si>
+  <si>
+    <t>CON-13 (Consent Decision Date/Time – DTM)</t>
+  </si>
+  <si>
+    <t>Consent.period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">period
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>Effective period for this Consent</t>
+  </si>
+  <si>
+    <t>Effective period for this Consent Resource and all provisions unless specified in that provision.</t>
+  </si>
+  <si>
+    <t>Consent.grantor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">grantor
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(CareTeam|HealthcareService|Organization|Patient|Practitioner|RelatedPerson|PractitionerRole)
+</t>
+  </si>
+  <si>
+    <t>Who is granting rights according to the policy and rules</t>
+  </si>
+  <si>
+    <t>The entity responsible for granting the rights listed in a Consent Directive.</t>
+  </si>
+  <si>
+    <t>Consent.grantee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">grantee
+</t>
+  </si>
+  <si>
+    <t>Who is agreeing to the policy and rules</t>
+  </si>
+  <si>
+    <t>The entity responsible for complying with the Consent Directive, including any obligations or limitations on authorizations and enforcement of prohibitions.</t>
+  </si>
+  <si>
+    <t>In a fully computable consent, both grantee and grantor  will be listed as actors within the consent. The Grantee and Grantor elements are for ease of search only.</t>
+  </si>
+  <si>
+    <t>Consent.manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">manager
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(HealthcareService|Organization|Patient|Practitioner)
+</t>
+  </si>
+  <si>
+    <t>Consent workflow management</t>
+  </si>
+  <si>
+    <t>The actor that manages the consent through its lifecycle.</t>
+  </si>
+  <si>
+    <t>FiveWs.witness</t>
+  </si>
+  <si>
+    <t>Consent.controller</t>
+  </si>
+  <si>
+    <t xml:space="preserve">controller
+</t>
+  </si>
+  <si>
+    <t>Consent Enforcer</t>
+  </si>
+  <si>
+    <t>The actor that controls/enforces the access according to the consent.</t>
+  </si>
+  <si>
+    <t>Consent.sourceAttachment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attachment
+</t>
+  </si>
+  <si>
+    <t>Source from which this consent is taken</t>
+  </si>
+  <si>
+    <t>The source on which this consent statement is based. The source might be a scanned original paper form.</t>
+  </si>
+  <si>
+    <t>The source can be contained inline (Attachment), referenced directly (Consent), referenced in a consent repository (DocumentReference), or simply by an identifier (Identifier), e.g. a CDA document id.</t>
+  </si>
+  <si>
+    <t>Potential mappings to CON-5,6,7,8,16,19, 20-23</t>
+  </si>
+  <si>
+    <t>Consent.sourceReference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Consent|DocumentReference|Contract|QuestionnaireResponse)
+</t>
+  </si>
+  <si>
+    <t>A reference to a consent that links back to such a source, a reference to a document repository (e.g. XDS) that stores the original consent document.</t>
+  </si>
+  <si>
+    <t>Consent.regulatoryBasis</t>
+  </si>
+  <si>
+    <t>Regulations establishing base Consent</t>
+  </si>
+  <si>
+    <t>A set of codes that indicate the regulatory basis (if any) that this consent supports.</t>
+  </si>
+  <si>
+    <t>Regulatory policy examples</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/consent-policy</t>
+  </si>
+  <si>
+    <t>CON-3 (Consent Form ID and Version – ST)
+Note: An implementation-specific requirement will be needed</t>
+  </si>
+  <si>
+    <t>Consent.policyBasis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BackboneElement
+</t>
+  </si>
+  <si>
+    <t>Computable version of the backing policy</t>
+  </si>
+  <si>
+    <t>A Reference or URL used to uniquely identify the policy the organization will enforce for this Consent. This Reference or URL should be specific to the version of the policy and should be dereferencable to a computable policy of some form.</t>
+  </si>
+  <si>
+    <t>Consent.policyBasis.id</t>
+  </si>
+  <si>
+    <t>Consent.policyBasis.extension</t>
+  </si>
+  <si>
+    <t>Consent.policyBasis.modifierExtension</t>
+  </si>
+  <si>
+    <t>extensions
+user contentmodifiers</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored even if unrecognized</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>BackboneElement.modifierExtension</t>
+  </si>
+  <si>
+    <t>Consent.policyBasis.reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Resource)
+</t>
+  </si>
+  <si>
+    <t>Reference backing policy resource</t>
+  </si>
+  <si>
+    <t>A Reference that identifies the policy the organization will enforce for this Consent.</t>
+  </si>
+  <si>
+    <t>While any resource may be used, Consent, PlanDefinition and Contract would be most frequent</t>
+  </si>
+  <si>
+    <t>Consent.policyBasis.url</t>
+  </si>
+  <si>
+    <t xml:space="preserve">url
+</t>
+  </si>
+  <si>
+    <t>URL to a computable backing policy</t>
+  </si>
+  <si>
+    <t>A URL that links to a computable version of the policy the organization will enforce for this Consent.</t>
+  </si>
+  <si>
+    <t>Consent.policyText</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(DocumentReference)
+</t>
+  </si>
+  <si>
+    <t>Human Readable Policy</t>
+  </si>
+  <si>
+    <t>A Reference to the human readable policy explaining the basis for the Consent.</t>
+  </si>
+  <si>
+    <t>Consent.verification</t>
+  </si>
+  <si>
+    <t>Consent Verified by patient or family</t>
+  </si>
+  <si>
+    <t>Whether a treatment instruction (e.g. artificial respiration: yes or no) was verified with the patient, his/her family or another authorized person.</t>
+  </si>
+  <si>
+    <t>Consent.verification.id</t>
+  </si>
+  <si>
+    <t>Consent.verification.extension</t>
+  </si>
+  <si>
+    <t>Consent.verification.modifierExtension</t>
+  </si>
+  <si>
+    <t>Consent.verification.verified</t>
   </si>
   <si>
     <t xml:space="preserve">boolean
 </t>
-  </si>
-  <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>Sometimes implied by being first</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
-    <t>Consent.category.text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>Consent.subject</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Patient)
-</t>
-  </si>
-  <si>
-    <t>Who the consent applies to</t>
-  </si>
-  <si>
-    <t>The patient/healthcare practitioner or group of persons to whom this consent applies.</t>
-  </si>
-  <si>
-    <t>Event.subject</t>
-  </si>
-  <si>
-    <t>FiveWs.subject[x]</t>
-  </si>
-  <si>
-    <t>Consent.date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">date
-</t>
-  </si>
-  <si>
-    <t>Fully executed date of the consent</t>
-  </si>
-  <si>
-    <t>Date the consent instance was agreed to.</t>
-  </si>
-  <si>
-    <t>Event.occurrence[x]</t>
-  </si>
-  <si>
-    <t>FiveWs.recorded</t>
-  </si>
-  <si>
-    <t>CON-13 (Consent Decision Date/Time – DTM)</t>
-  </si>
-  <si>
-    <t>Consent.period</t>
-  </si>
-  <si>
-    <t xml:space="preserve">period
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Period
-</t>
-  </si>
-  <si>
-    <t>Effective period for this Consent</t>
-  </si>
-  <si>
-    <t>Effective period for this Consent Resource and all provisions unless specified in that provision.</t>
-  </si>
-  <si>
-    <t>Consent.grantor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">grantor
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(CareTeam|HealthcareService|Organization|Patient|Practitioner|RelatedPerson|PractitionerRole)
-</t>
-  </si>
-  <si>
-    <t>Who is granting rights according to the policy and rules</t>
-  </si>
-  <si>
-    <t>The entity responsible for granting the rights listed in a Consent Directive.</t>
-  </si>
-  <si>
-    <t>Consent.grantee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">grantee
-</t>
-  </si>
-  <si>
-    <t>Who is agreeing to the policy and rules</t>
-  </si>
-  <si>
-    <t>The entity responsible for complying with the Consent Directive, including any obligations or limitations on authorizations and enforcement of prohibitions.</t>
-  </si>
-  <si>
-    <t>In a fully computable consent, both grantee and grantor  will be listed as actors within the consent. The Grantee and Grantor elements are for ease of search only.</t>
-  </si>
-  <si>
-    <t>Consent.manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">manager
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(HealthcareService|Organization|Patient|Practitioner)
-</t>
-  </si>
-  <si>
-    <t>Consent workflow management</t>
-  </si>
-  <si>
-    <t>The actor that manages the consent through its lifecycle.</t>
-  </si>
-  <si>
-    <t>FiveWs.witness</t>
-  </si>
-  <si>
-    <t>Consent.controller</t>
-  </si>
-  <si>
-    <t xml:space="preserve">controller
-</t>
-  </si>
-  <si>
-    <t>Consent Enforcer</t>
-  </si>
-  <si>
-    <t>The actor that controls/enforces the access according to the consent.</t>
-  </si>
-  <si>
-    <t>Consent.sourceAttachment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Attachment
-</t>
-  </si>
-  <si>
-    <t>Source from which this consent is taken</t>
-  </si>
-  <si>
-    <t>The source on which this consent statement is based. The source might be a scanned original paper form.</t>
-  </si>
-  <si>
-    <t>The source can be contained inline (Attachment), referenced directly (Consent), referenced in a consent repository (DocumentReference), or simply by an identifier (Identifier), e.g. a CDA document id.</t>
-  </si>
-  <si>
-    <t>Potential mappings to CON-5,6,7,8,16,19, 20-23</t>
-  </si>
-  <si>
-    <t>Consent.sourceReference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Consent|DocumentReference|Contract|QuestionnaireResponse)
-</t>
-  </si>
-  <si>
-    <t>A reference to a consent that links back to such a source, a reference to a document repository (e.g. XDS) that stores the original consent document.</t>
-  </si>
-  <si>
-    <t>Consent.regulatoryBasis</t>
-  </si>
-  <si>
-    <t>Regulations establishing base Consent</t>
-  </si>
-  <si>
-    <t>A set of codes that indicate the regulatory basis (if any) that this consent supports.</t>
-  </si>
-  <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ValueSet/vs-patient-consent-for-sms-notifications</t>
-  </si>
-  <si>
-    <t>CON-3 (Consent Form ID and Version – ST)
-Note: An implementation-specific requirement will be needed</t>
-  </si>
-  <si>
-    <t>Consent.regulatoryBasis.id</t>
-  </si>
-  <si>
-    <t>Consent.regulatoryBasis.extension</t>
-  </si>
-  <si>
-    <t>Consent.regulatoryBasis.coding</t>
-  </si>
-  <si>
-    <t>Consent.regulatoryBasis.text</t>
-  </si>
-  <si>
-    <t>Consent policy</t>
-  </si>
-  <si>
-    <t>Consent.policyBasis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BackboneElement
-</t>
-  </si>
-  <si>
-    <t>Computable version of the backing policy</t>
-  </si>
-  <si>
-    <t>A Reference or URL used to uniquely identify the policy the organization will enforce for this Consent. This Reference or URL should be specific to the version of the policy and should be dereferencable to a computable policy of some form.</t>
-  </si>
-  <si>
-    <t>Consent.policyBasis.id</t>
-  </si>
-  <si>
-    <t>Consent.policyBasis.extension</t>
-  </si>
-  <si>
-    <t>Consent.policyBasis.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user contentmodifiers</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>BackboneElement.modifierExtension</t>
-  </si>
-  <si>
-    <t>Consent.policyBasis.reference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Resource)
-</t>
-  </si>
-  <si>
-    <t>Reference backing policy resource</t>
-  </si>
-  <si>
-    <t>A Reference that identifies the policy the organization will enforce for this Consent.</t>
-  </si>
-  <si>
-    <t>While any resource may be used, Consent, PlanDefinition and Contract would be most frequent</t>
-  </si>
-  <si>
-    <t>Consent.policyBasis.url</t>
-  </si>
-  <si>
-    <t xml:space="preserve">url
-</t>
-  </si>
-  <si>
-    <t>URL to a computable backing policy</t>
-  </si>
-  <si>
-    <t>A URL that links to a computable version of the policy the organization will enforce for this Consent.</t>
-  </si>
-  <si>
-    <t>Consent.policyText</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(DocumentReference)
-</t>
-  </si>
-  <si>
-    <t>Human Readable Policy</t>
-  </si>
-  <si>
-    <t>A Reference to the human readable policy explaining the basis for the Consent.</t>
-  </si>
-  <si>
-    <t>Consent.verification</t>
-  </si>
-  <si>
-    <t>Consent Verified by patient or family</t>
-  </si>
-  <si>
-    <t>Whether a treatment instruction (e.g. artificial respiration: yes or no) was verified with the patient, his/her family or another authorized person.</t>
-  </si>
-  <si>
-    <t>Consent.verification.id</t>
-  </si>
-  <si>
-    <t>Consent.verification.extension</t>
-  </si>
-  <si>
-    <t>Consent.verification.modifierExtension</t>
-  </si>
-  <si>
-    <t>Consent.verification.verified</t>
   </si>
   <si>
     <t>Has been verified</t>
@@ -1733,7 +1605,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN81"/>
+  <dimension ref="A1:AN70"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="40.04296875" customWidth="true" bestFit="true"/>
@@ -1761,7 +1633,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="125.95703125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="78.23828125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="52.5703125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -3199,7 +3071,7 @@
         <v>77</v>
       </c>
       <c r="S13" t="s" s="2">
-        <v>77</v>
+        <v>169</v>
       </c>
       <c r="T13" t="s" s="2">
         <v>77</v>
@@ -3214,13 +3086,13 @@
         <v>77</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>77</v>
@@ -3253,13 +3125,13 @@
         <v>101</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>77</v>
@@ -3267,10 +3139,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3296,10 +3168,10 @@
         <v>91</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3350,7 +3222,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3359,7 +3231,7 @@
         <v>89</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>77</v>
@@ -3374,15 +3246,15 @@
         <v>77</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3411,7 +3283,7 @@
         <v>138</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N15" t="s" s="2">
         <v>140</v>
@@ -3452,19 +3324,19 @@
         <v>77</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AD15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3488,15 +3360,15 @@
         <v>77</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3519,19 +3391,19 @@
         <v>90</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>77</v>
@@ -3580,7 +3452,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3601,18 +3473,18 @@
         <v>77</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3632,19 +3504,23 @@
         <v>77</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>91</v>
+        <v>198</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>176</v>
+        <v>199</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
+        <v>200</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="O17" t="s" s="2">
+        <v>202</v>
+      </c>
       <c r="P17" t="s" s="2">
         <v>77</v>
       </c>
@@ -3653,7 +3529,7 @@
         <v>77</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>77</v>
+        <v>203</v>
       </c>
       <c r="T17" t="s" s="2">
         <v>77</v>
@@ -3692,7 +3568,7 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>178</v>
+        <v>204</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3701,10 +3577,10 @@
         <v>89</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>179</v>
+        <v>77</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>77</v>
@@ -3713,29 +3589,29 @@
         <v>77</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>77</v>
+        <v>205</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>180</v>
+        <v>206</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>136</v>
+        <v>77</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>77</v>
@@ -3744,20 +3620,18 @@
         <v>77</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>137</v>
+        <v>208</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>138</v>
+        <v>209</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>77</v>
@@ -3794,51 +3668,51 @@
         <v>77</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>183</v>
+        <v>77</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>184</v>
+        <v>77</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>185</v>
+        <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>186</v>
+        <v>207</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>77</v>
+        <v>211</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>77</v>
+        <v>212</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>180</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3861,20 +3735,16 @@
         <v>90</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>103</v>
+        <v>214</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>199</v>
+        <v>215</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>202</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>77</v>
       </c>
@@ -3883,7 +3753,7 @@
         <v>77</v>
       </c>
       <c r="S19" t="s" s="2">
-        <v>203</v>
+        <v>77</v>
       </c>
       <c r="T19" t="s" s="2">
         <v>77</v>
@@ -3922,7 +3792,7 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3937,28 +3807,28 @@
         <v>101</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>77</v>
+        <v>217</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>77</v>
+        <v>218</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>206</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>77</v>
+        <v>221</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3977,17 +3847,15 @@
         <v>90</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>211</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>77</v>
@@ -4036,7 +3904,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -4057,29 +3925,29 @@
         <v>77</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>213</v>
+        <v>77</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>214</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>77</v>
+        <v>226</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>77</v>
@@ -4091,18 +3959,16 @@
         <v>90</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>109</v>
+        <v>227</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="N21" s="2"/>
-      <c r="O21" t="s" s="2">
-        <v>218</v>
-      </c>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>77</v>
       </c>
@@ -4111,7 +3977,7 @@
         <v>77</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>219</v>
+        <v>77</v>
       </c>
       <c r="T21" t="s" s="2">
         <v>77</v>
@@ -4150,16 +4016,16 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>221</v>
+        <v>77</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>101</v>
@@ -4171,29 +4037,29 @@
         <v>77</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>222</v>
+        <v>77</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>223</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>77</v>
+        <v>231</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>77</v>
@@ -4205,18 +4071,18 @@
         <v>90</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="N22" s="2"/>
-      <c r="O22" t="s" s="2">
-        <v>227</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>77</v>
       </c>
@@ -4264,16 +4130,16 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>221</v>
+        <v>77</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>101</v>
@@ -4285,29 +4151,29 @@
         <v>77</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>229</v>
+        <v>77</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>230</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>77</v>
+        <v>236</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>77</v>
@@ -4316,23 +4182,19 @@
         <v>77</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>236</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>77</v>
       </c>
@@ -4380,13 +4242,13 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>77</v>
@@ -4398,32 +4260,32 @@
         <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>77</v>
+        <v>240</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>238</v>
+        <v>77</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>239</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>77</v>
+        <v>242</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>77</v>
@@ -4432,23 +4294,19 @@
         <v>77</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>208</v>
+        <v>237</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="O24" t="s" s="2">
         <v>244</v>
       </c>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>77</v>
       </c>
@@ -4496,13 +4354,13 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>77</v>
@@ -4517,18 +4375,18 @@
         <v>77</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>246</v>
+        <v>77</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>247</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4536,10 +4394,10 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>77</v>
@@ -4548,18 +4406,20 @@
         <v>77</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="N25" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="L25" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4608,13 +4468,13 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>77</v>
@@ -4623,13 +4483,13 @@
         <v>101</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>252</v>
+        <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>253</v>
+        <v>77</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>77</v>
+        <v>250</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>77</v>
@@ -4637,10 +4497,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4651,7 +4511,7 @@
         <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>77</v>
@@ -4660,18 +4520,20 @@
         <v>77</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>253</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>249</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -4720,13 +4582,13 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>77</v>
@@ -4735,13 +4597,13 @@
         <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>258</v>
+        <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>259</v>
+        <v>77</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>77</v>
@@ -4749,21 +4611,21 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>262</v>
+        <v>77</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>77</v>
@@ -4772,16 +4634,16 @@
         <v>77</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>263</v>
+        <v>166</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4808,13 +4670,13 @@
         <v>77</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>77</v>
+        <v>170</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>77</v>
+        <v>257</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>77</v>
+        <v>258</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>77</v>
@@ -4832,13 +4694,13 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>77</v>
@@ -4853,7 +4715,7 @@
         <v>77</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>77</v>
+        <v>259</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>77</v>
@@ -4861,21 +4723,21 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>267</v>
+        <v>77</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>77</v>
@@ -4884,16 +4746,16 @@
         <v>77</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4944,13 +4806,13 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>77</v>
@@ -4973,21 +4835,21 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>272</v>
+        <v>77</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>77</v>
@@ -4996,20 +4858,18 @@
         <v>77</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>268</v>
+        <v>198</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>273</v>
+        <v>177</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>275</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>77</v>
@@ -5058,19 +4918,19 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>271</v>
+        <v>179</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>77</v>
+        <v>180</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>77</v>
@@ -5082,19 +4942,19 @@
         <v>77</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>77</v>
+        <v>181</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>277</v>
+        <v>136</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5113,15 +4973,17 @@
         <v>77</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>278</v>
+        <v>137</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>279</v>
+        <v>138</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>183</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>77</v>
@@ -5170,7 +5032,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>276</v>
+        <v>187</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5182,31 +5044,31 @@
         <v>77</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>281</v>
+        <v>77</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>77</v>
+        <v>181</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>282</v>
+        <v>266</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>282</v>
+        <v>266</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5219,22 +5081,26 @@
         <v>77</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>278</v>
+        <v>137</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>284</v>
+        <v>268</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
+        <v>269</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>77</v>
       </c>
@@ -5282,7 +5148,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5294,7 +5160,7 @@
         <v>77</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>77</v>
@@ -5306,15 +5172,15 @@
         <v>77</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>77</v>
+        <v>134</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>286</v>
+        <v>271</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>286</v>
+        <v>271</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5325,7 +5191,7 @@
         <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>77</v>
@@ -5337,16 +5203,16 @@
         <v>77</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>287</v>
+        <v>272</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>289</v>
+        <v>274</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>290</v>
+        <v>275</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5396,13 +5262,13 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>286</v>
+        <v>271</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>77</v>
@@ -5417,7 +5283,7 @@
         <v>77</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>291</v>
+        <v>77</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>77</v>
@@ -5425,10 +5291,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5439,7 +5305,7 @@
         <v>78</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>77</v>
@@ -5451,17 +5317,15 @@
         <v>77</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>293</v>
+        <v>277</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -5510,13 +5374,13 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>77</v>
@@ -5531,7 +5395,7 @@
         <v>77</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>291</v>
+        <v>77</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>77</v>
@@ -5539,10 +5403,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>295</v>
+        <v>280</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>295</v>
+        <v>280</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5550,10 +5414,10 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>77</v>
@@ -5565,13 +5429,13 @@
         <v>77</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>166</v>
+        <v>281</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>296</v>
+        <v>282</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>297</v>
+        <v>283</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5598,11 +5462,13 @@
         <v>77</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="Y34" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z34" t="s" s="2">
-        <v>298</v>
+        <v>77</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>77</v>
@@ -5620,7 +5486,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>295</v>
+        <v>280</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5641,7 +5507,7 @@
         <v>77</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>299</v>
+        <v>77</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>77</v>
@@ -5649,10 +5515,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>300</v>
+        <v>284</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>300</v>
+        <v>284</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5663,7 +5529,7 @@
         <v>78</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>77</v>
@@ -5672,16 +5538,16 @@
         <v>77</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>91</v>
+        <v>261</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>176</v>
+        <v>285</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>177</v>
+        <v>286</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5732,19 +5598,19 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>178</v>
+        <v>284</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>179</v>
+        <v>77</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>77</v>
@@ -5756,26 +5622,26 @@
         <v>77</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>180</v>
+        <v>77</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>301</v>
+        <v>287</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>301</v>
+        <v>287</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>136</v>
+        <v>77</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>77</v>
@@ -5787,17 +5653,15 @@
         <v>77</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>137</v>
+        <v>198</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>138</v>
+        <v>177</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -5834,31 +5698,31 @@
         <v>77</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>183</v>
+        <v>77</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>184</v>
+        <v>77</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>185</v>
+        <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>77</v>
+        <v>180</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>142</v>
+        <v>77</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>77</v>
@@ -5870,19 +5734,19 @@
         <v>77</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>302</v>
+        <v>288</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>302</v>
+        <v>288</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -5898,23 +5762,21 @@
         <v>77</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>188</v>
+        <v>137</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>189</v>
+        <v>138</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>192</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>77</v>
       </c>
@@ -5962,7 +5824,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5974,7 +5836,7 @@
         <v>77</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>77</v>
@@ -5983,53 +5845,53 @@
         <v>77</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>194</v>
+        <v>77</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>195</v>
+        <v>181</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>303</v>
+        <v>289</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>303</v>
+        <v>289</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>77</v>
+        <v>267</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="J38" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>208</v>
+        <v>137</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>241</v>
+        <v>268</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>242</v>
+        <v>269</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>243</v>
+        <v>140</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>244</v>
+        <v>146</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>77</v>
@@ -6039,7 +5901,7 @@
         <v>77</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>304</v>
+        <v>77</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>77</v>
@@ -6078,19 +5940,19 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>77</v>
@@ -6099,18 +5961,18 @@
         <v>77</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>246</v>
+        <v>77</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>247</v>
+        <v>134</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6118,7 +5980,7 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>89</v>
@@ -6130,16 +5992,16 @@
         <v>77</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>306</v>
+        <v>291</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>308</v>
+        <v>293</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6190,10 +6052,10 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>89</v>
@@ -6219,10 +6081,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>309</v>
+        <v>294</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>309</v>
+        <v>294</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6245,15 +6107,17 @@
         <v>77</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>208</v>
+        <v>166</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>176</v>
+        <v>295</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>296</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>297</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>77</v>
@@ -6278,13 +6142,13 @@
         <v>77</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>77</v>
+        <v>170</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>77</v>
+        <v>298</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>77</v>
+        <v>299</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>77</v>
@@ -6302,7 +6166,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>178</v>
+        <v>294</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6311,10 +6175,10 @@
         <v>89</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>179</v>
+        <v>77</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>77</v>
@@ -6326,26 +6190,26 @@
         <v>77</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>180</v>
+        <v>77</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>136</v>
+        <v>77</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>77</v>
@@ -6357,17 +6221,15 @@
         <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>137</v>
+        <v>301</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>138</v>
+        <v>302</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>77</v>
@@ -6416,19 +6278,19 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>186</v>
+        <v>300</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>77</v>
@@ -6440,51 +6302,47 @@
         <v>77</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>180</v>
+        <v>77</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>312</v>
+        <v>77</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>137</v>
+        <v>305</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>307</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>77</v>
       </c>
@@ -6532,19 +6390,19 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>77</v>
@@ -6556,15 +6414,15 @@
         <v>77</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>134</v>
+        <v>77</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6575,7 +6433,7 @@
         <v>78</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>77</v>
@@ -6587,16 +6445,16 @@
         <v>77</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6646,13 +6504,13 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>77</v>
@@ -6675,10 +6533,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6686,7 +6544,7 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>89</v>
@@ -6695,19 +6553,19 @@
         <v>77</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>322</v>
+        <v>109</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6734,13 +6592,13 @@
         <v>77</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>77</v>
+        <v>316</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>77</v>
+        <v>317</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>77</v>
@@ -6758,7 +6616,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6787,10 +6645,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6810,16 +6668,16 @@
         <v>77</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>326</v>
+        <v>261</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6870,7 +6728,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6899,10 +6757,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6913,7 +6771,7 @@
         <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>77</v>
@@ -6922,16 +6780,16 @@
         <v>77</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>306</v>
+        <v>198</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>330</v>
+        <v>177</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>331</v>
+        <v>178</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6982,19 +6840,19 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>329</v>
+        <v>179</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>77</v>
+        <v>180</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>77</v>
@@ -7006,26 +6864,26 @@
         <v>77</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>77</v>
+        <v>181</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>77</v>
@@ -7037,15 +6895,17 @@
         <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>208</v>
+        <v>137</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>176</v>
+        <v>138</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>183</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>77</v>
@@ -7094,19 +6954,19 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>179</v>
+        <v>77</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>77</v>
+        <v>142</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>77</v>
@@ -7118,19 +6978,19 @@
         <v>77</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>136</v>
+        <v>267</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7143,24 +7003,26 @@
         <v>77</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K48" t="s" s="2">
         <v>137</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>138</v>
+        <v>268</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>182</v>
+        <v>269</v>
       </c>
       <c r="N48" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="O48" s="2"/>
+      <c r="O48" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>77</v>
       </c>
@@ -7208,7 +7070,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>186</v>
+        <v>270</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7232,51 +7094,49 @@
         <v>77</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>180</v>
+        <v>134</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>312</v>
+        <v>77</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="J49" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>137</v>
+        <v>222</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>327</v>
+      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>77</v>
       </c>
@@ -7324,19 +7184,19 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>77</v>
@@ -7345,18 +7205,18 @@
         <v>77</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>77</v>
+        <v>328</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>134</v>
+        <v>77</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7364,10 +7224,10 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>77</v>
@@ -7376,23 +7236,25 @@
         <v>77</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>232</v>
+        <v>261</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q50" s="2"/>
+      <c r="Q50" t="s" s="2">
+        <v>332</v>
+      </c>
       <c r="R50" t="s" s="2">
         <v>77</v>
       </c>
@@ -7436,13 +7298,13 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>77</v>
@@ -7465,10 +7327,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7491,17 +7353,15 @@
         <v>77</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>166</v>
+        <v>198</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>339</v>
+        <v>177</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>341</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>77</v>
@@ -7526,13 +7386,13 @@
         <v>77</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>169</v>
+        <v>77</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>342</v>
+        <v>77</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>343</v>
+        <v>77</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>77</v>
@@ -7550,7 +7410,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>338</v>
+        <v>179</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7559,10 +7419,10 @@
         <v>89</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>77</v>
+        <v>180</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>77</v>
@@ -7574,26 +7434,26 @@
         <v>77</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>77</v>
+        <v>181</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>77</v>
@@ -7605,15 +7465,17 @@
         <v>77</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>345</v>
+        <v>137</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>346</v>
+        <v>138</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>183</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>77</v>
@@ -7662,19 +7524,19 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>344</v>
+        <v>187</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>77</v>
@@ -7686,47 +7548,51 @@
         <v>77</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>77</v>
+        <v>181</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>77</v>
+        <v>267</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>349</v>
+        <v>137</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>350</v>
+        <v>268</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
+        <v>269</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>77</v>
       </c>
@@ -7774,19 +7640,19 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>348</v>
+        <v>270</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>77</v>
@@ -7798,15 +7664,15 @@
         <v>77</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>77</v>
+        <v>134</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7817,7 +7683,7 @@
         <v>78</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>77</v>
@@ -7829,17 +7695,15 @@
         <v>77</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>353</v>
+        <v>166</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>354</v>
+        <v>337</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>356</v>
-      </c>
+        <v>338</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>77</v>
@@ -7864,13 +7728,13 @@
         <v>77</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>77</v>
+        <v>339</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>77</v>
+        <v>340</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>77</v>
+        <v>341</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>77</v>
@@ -7888,13 +7752,13 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>77</v>
@@ -7917,10 +7781,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7928,7 +7792,7 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>89</v>
@@ -7937,19 +7801,19 @@
         <v>77</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>109</v>
+        <v>343</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>358</v>
+        <v>344</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>359</v>
+        <v>345</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7976,13 +7840,13 @@
         <v>77</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>360</v>
+        <v>77</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>361</v>
+        <v>77</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>77</v>
@@ -8000,7 +7864,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8029,10 +7893,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>362</v>
+        <v>346</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>362</v>
+        <v>346</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8055,20 +7919,24 @@
         <v>90</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>306</v>
+        <v>166</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>363</v>
+        <v>347</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>348</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>349</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q56" s="2"/>
+      <c r="Q56" t="s" s="2">
+        <v>350</v>
+      </c>
       <c r="R56" t="s" s="2">
         <v>77</v>
       </c>
@@ -8088,13 +7956,13 @@
         <v>77</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>77</v>
+        <v>170</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>77</v>
+        <v>351</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>77</v>
+        <v>352</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>77</v>
@@ -8112,7 +7980,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>362</v>
+        <v>346</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8141,10 +8009,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>365</v>
+        <v>353</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>365</v>
+        <v>353</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8155,7 +8023,7 @@
         <v>78</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>77</v>
@@ -8164,18 +8032,20 @@
         <v>77</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>208</v>
+        <v>189</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>176</v>
+        <v>354</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="N57" s="2"/>
+        <v>355</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>356</v>
+      </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>77</v>
@@ -8200,13 +8070,13 @@
         <v>77</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>77</v>
+        <v>170</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>77</v>
+        <v>357</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>77</v>
+        <v>358</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>77</v>
@@ -8224,19 +8094,19 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>178</v>
+        <v>353</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>179</v>
+        <v>77</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>77</v>
@@ -8248,19 +8118,19 @@
         <v>77</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>180</v>
+        <v>77</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>136</v>
+        <v>77</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8276,19 +8146,19 @@
         <v>77</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>137</v>
+        <v>189</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>138</v>
+        <v>360</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>182</v>
+        <v>361</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>140</v>
+        <v>362</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8314,13 +8184,13 @@
         <v>77</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>77</v>
+        <v>339</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>77</v>
+        <v>363</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>77</v>
+        <v>364</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>77</v>
@@ -8338,7 +8208,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>186</v>
+        <v>359</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8350,7 +8220,7 @@
         <v>77</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>77</v>
@@ -8362,19 +8232,19 @@
         <v>77</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>180</v>
+        <v>77</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>312</v>
+        <v>77</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8387,26 +8257,24 @@
         <v>77</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="J59" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>137</v>
+        <v>189</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>313</v>
+        <v>366</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>314</v>
+        <v>367</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>368</v>
+      </c>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>77</v>
       </c>
@@ -8430,13 +8298,13 @@
         <v>77</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>77</v>
+        <v>369</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>77</v>
+        <v>370</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>77</v>
+        <v>371</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>77</v>
@@ -8454,7 +8322,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>315</v>
+        <v>365</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8466,7 +8334,7 @@
         <v>77</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>77</v>
@@ -8478,15 +8346,15 @@
         <v>77</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>134</v>
+        <v>77</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8497,7 +8365,7 @@
         <v>78</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>77</v>
@@ -8509,16 +8377,16 @@
         <v>90</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>263</v>
+        <v>189</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8544,13 +8412,13 @@
         <v>77</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>77</v>
+        <v>339</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>77</v>
+        <v>376</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>77</v>
+        <v>377</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>77</v>
@@ -8568,13 +8436,13 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>77</v>
@@ -8589,7 +8457,7 @@
         <v>77</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>372</v>
+        <v>77</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>77</v>
@@ -8597,10 +8465,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8620,25 +8488,23 @@
         <v>77</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>306</v>
+        <v>166</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q61" t="s" s="2">
-        <v>376</v>
-      </c>
+      <c r="Q61" s="2"/>
       <c r="R61" t="s" s="2">
         <v>77</v>
       </c>
@@ -8658,13 +8524,13 @@
         <v>77</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>77</v>
+        <v>170</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>77</v>
+        <v>381</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>77</v>
+        <v>382</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>77</v>
@@ -8682,7 +8548,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8711,10 +8577,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8734,18 +8600,20 @@
         <v>77</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>176</v>
+        <v>384</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="N62" s="2"/>
+        <v>385</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>386</v>
+      </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>77</v>
@@ -8794,7 +8662,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>178</v>
+        <v>383</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -8803,10 +8671,10 @@
         <v>89</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>179</v>
+        <v>77</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>77</v>
@@ -8818,19 +8686,19 @@
         <v>77</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>180</v>
+        <v>77</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>136</v>
+        <v>77</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -8846,25 +8714,25 @@
         <v>77</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>137</v>
+        <v>261</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>138</v>
+        <v>388</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>389</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q63" s="2"/>
+      <c r="Q63" t="s" s="2">
+        <v>390</v>
+      </c>
       <c r="R63" t="s" s="2">
         <v>77</v>
       </c>
@@ -8908,7 +8776,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>186</v>
+        <v>387</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -8920,7 +8788,7 @@
         <v>77</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>77</v>
@@ -8932,51 +8800,47 @@
         <v>77</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>180</v>
+        <v>77</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>312</v>
+        <v>77</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>137</v>
+        <v>198</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>313</v>
+        <v>177</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>77</v>
       </c>
@@ -9024,19 +8888,19 @@
         <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>315</v>
+        <v>179</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>77</v>
+        <v>180</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>142</v>
+        <v>77</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>77</v>
@@ -9048,26 +8912,26 @@
         <v>77</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>134</v>
+        <v>181</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>77</v>
@@ -9079,15 +8943,17 @@
         <v>77</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>166</v>
+        <v>137</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>381</v>
+        <v>138</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N65" s="2"/>
+        <v>183</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>77</v>
@@ -9112,13 +8978,13 @@
         <v>77</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>383</v>
+        <v>77</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>384</v>
+        <v>77</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>385</v>
+        <v>77</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>77</v>
@@ -9136,19 +9002,19 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>380</v>
+        <v>187</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>77</v>
@@ -9160,47 +9026,51 @@
         <v>77</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>77</v>
+        <v>181</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>77</v>
+        <v>267</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>387</v>
+        <v>137</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>388</v>
+        <v>268</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
+        <v>269</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>77</v>
       </c>
@@ -9248,19 +9118,19 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>386</v>
+        <v>270</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>77</v>
@@ -9272,15 +9142,15 @@
         <v>77</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>77</v>
+        <v>134</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9288,10 +9158,10 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>77</v>
@@ -9303,74 +9173,70 @@
         <v>90</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>166</v>
+        <v>109</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>393</v>
-      </c>
+        <v>396</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q67" t="s" s="2">
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF67" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="R67" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S67" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T67" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U67" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V67" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W67" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X67" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="Y67" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="Z67" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="AA67" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB67" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>390</v>
-      </c>
       <c r="AG67" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>77</v>
@@ -9393,10 +9259,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9404,10 +9270,10 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>77</v>
@@ -9419,17 +9285,15 @@
         <v>90</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>188</v>
+        <v>272</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>400</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>77</v>
@@ -9454,13 +9318,13 @@
         <v>77</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>169</v>
+        <v>77</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>401</v>
+        <v>77</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>402</v>
+        <v>77</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>77</v>
@@ -9478,13 +9342,13 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>77</v>
@@ -9507,10 +9371,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9521,7 +9385,7 @@
         <v>78</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>77</v>
@@ -9530,10 +9394,10 @@
         <v>77</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>188</v>
+        <v>403</v>
       </c>
       <c r="L69" t="s" s="2">
         <v>404</v>
@@ -9568,13 +9432,13 @@
         <v>77</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>383</v>
+        <v>77</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>407</v>
+        <v>77</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>408</v>
+        <v>77</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>77</v>
@@ -9592,13 +9456,13 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>77</v>
@@ -9621,10 +9485,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9644,20 +9508,18 @@
         <v>77</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>188</v>
+        <v>80</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>412</v>
-      </c>
+        <v>409</v>
+      </c>
+      <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>77</v>
@@ -9682,13 +9544,13 @@
         <v>77</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>413</v>
+        <v>77</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>414</v>
+        <v>77</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>415</v>
+        <v>77</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>77</v>
@@ -9706,7 +9568,7 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -9730,1252 +9592,6 @@
         <v>77</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="C71" s="2"/>
-      <c r="D71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E71" s="2"/>
-      <c r="F71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J71" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K71" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="L71" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="O71" s="2"/>
-      <c r="P71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q71" s="2"/>
-      <c r="R71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X71" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="Y71" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="Z71" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="AG71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ71" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="C72" s="2"/>
-      <c r="D72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E72" s="2"/>
-      <c r="F72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J72" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K72" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="L72" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="N72" s="2"/>
-      <c r="O72" s="2"/>
-      <c r="P72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q72" s="2"/>
-      <c r="R72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X72" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="Y72" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="Z72" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="AG72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ72" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="C73" s="2"/>
-      <c r="D73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E73" s="2"/>
-      <c r="F73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G73" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J73" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K73" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="L73" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="O73" s="2"/>
-      <c r="P73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q73" s="2"/>
-      <c r="R73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="AG73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH73" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ73" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN73" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="B74" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="C74" s="2"/>
-      <c r="D74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E74" s="2"/>
-      <c r="F74" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J74" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K74" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="L74" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="N74" s="2"/>
-      <c r="O74" s="2"/>
-      <c r="P74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q74" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="R74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="AG74" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ74" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="B75" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="C75" s="2"/>
-      <c r="D75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E75" s="2"/>
-      <c r="F75" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G75" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K75" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="L75" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="N75" s="2"/>
-      <c r="O75" s="2"/>
-      <c r="P75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q75" s="2"/>
-      <c r="R75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF75" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="AG75" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH75" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI75" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="AJ75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="B76" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="C76" s="2"/>
-      <c r="D76" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="E76" s="2"/>
-      <c r="F76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H76" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I76" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J76" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K76" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="L76" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O76" s="2"/>
-      <c r="P76" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q76" s="2"/>
-      <c r="R76" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S76" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T76" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U76" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V76" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W76" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X76" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y76" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z76" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="AG76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI76" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ76" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK76" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL76" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="C77" s="2"/>
-      <c r="D77" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="E77" s="2"/>
-      <c r="F77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H77" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I77" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="J77" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K77" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="L77" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="P77" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q77" s="2"/>
-      <c r="R77" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S77" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T77" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U77" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V77" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W77" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X77" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y77" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z77" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF77" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="AG77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI77" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ77" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK77" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL77" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM77" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN77" t="s" s="2">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="B78" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="C78" s="2"/>
-      <c r="D78" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E78" s="2"/>
-      <c r="F78" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="G78" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H78" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I78" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J78" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K78" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="L78" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N78" s="2"/>
-      <c r="O78" s="2"/>
-      <c r="P78" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q78" s="2"/>
-      <c r="R78" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S78" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T78" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U78" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V78" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W78" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X78" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="Y78" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="Z78" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="AA78" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB78" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD78" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE78" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF78" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="AG78" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH78" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI78" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ78" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK78" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL78" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM78" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="B79" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="C79" s="2"/>
-      <c r="D79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E79" s="2"/>
-      <c r="F79" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="G79" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J79" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K79" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="L79" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="N79" s="2"/>
-      <c r="O79" s="2"/>
-      <c r="P79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q79" s="2"/>
-      <c r="R79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF79" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="AG79" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH79" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ79" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN79" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="B80" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="C80" s="2"/>
-      <c r="D80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E80" s="2"/>
-      <c r="F80" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G80" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K80" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="L80" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="O80" s="2"/>
-      <c r="P80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q80" s="2"/>
-      <c r="R80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF80" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="AG80" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH80" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ80" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN80" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="B81" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="C81" s="2"/>
-      <c r="D81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E81" s="2"/>
-      <c r="F81" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K81" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="L81" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="N81" s="2"/>
-      <c r="O81" s="2"/>
-      <c r="P81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q81" s="2"/>
-      <c r="R81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF81" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="AG81" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ81" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN81" t="s" s="2">
         <v>77</v>
       </c>
     </row>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:26:59+00:00</t>
+    <t>2023-05-12T10:27:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:27:50+00:00</t>
+    <t>2023-05-12T10:32:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:32:06+00:00</t>
+    <t>2023-05-12T10:40:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:40:31+00:00</t>
+    <t>2023-05-12T13:37:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T13:37:18+00:00</t>
+    <t>2023-05-12T13:51:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T13:51:30+00:00</t>
+    <t>2023-05-23T09:07:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-23T09:07:38+00:00</t>
+    <t>2023-05-23T09:13:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
